--- a/server/templates/SMP-Visualisation-NonResidential.xlsx
+++ b/server/templates/SMP-Visualisation-NonResidential.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amina_0soxtza\Dropbox\GIW TEAM\GIW\8_Templates\Calculator Templates\SMP Visualisation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inesb\Desktop\Claude Code\server\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FFA123-2A86-41DC-879A-A36D1655A49E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D12397D0-4769-470E-8B66-5A0E3931BFA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3C857329-8C44-458F-A49B-D8C19524634F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3C857329-8C44-458F-A49B-D8C19524634F}"/>
   </bookViews>
   <sheets>
     <sheet name="Final Report" sheetId="12" r:id="rId1"/>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="244">
   <si>
     <t>Development</t>
   </si>
@@ -865,9 +865,6 @@
     <t>Lift</t>
   </si>
   <si>
-    <t>123 Address</t>
-  </si>
-  <si>
     <t>Heating &amp; Cooling 
 (Gas)</t>
   </si>
@@ -1515,14 +1512,17 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="13" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="13" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -1530,19 +1530,7 @@
     <xf numFmtId="3" fontId="13" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="8" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1557,10 +1545,13 @@
     <xf numFmtId="0" fontId="9" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1570,6 +1561,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1811,7 +1808,7 @@
                 <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>241460.52585061869</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1831,7 +1828,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1944,7 +1941,7 @@
                 <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>136463.84117365969</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2226,7 +2223,7 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1298.9119338286555</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -2235,13 +2232,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12058.199999999999</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6373.1849999999986</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2261,7 +2258,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2309,7 +2306,7 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1184.3020573143624</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -2318,13 +2315,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12058.199999999999</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6373.1849999999986</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2676,7 +2673,7 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1298.9119338286555</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -2685,13 +2682,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12058.199999999999</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6373.1849999999986</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2711,7 +2708,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2759,7 +2756,7 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1184.3020573143624</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -2768,13 +2765,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12058.199999999999</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6373.1849999999986</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3103,25 +3100,25 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>338427.68153202703</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>218748.6</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>193701.2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>34406.641250000001</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7738.8674999999985</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7393.7999999999993</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3141,7 +3138,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3196,25 +3193,25 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>307684.06257331884</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>81249.48000000001</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>34833.199999999997</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20999.406499999997</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7738.8674999999985</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7393.7999999999993</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3567,7 +3564,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3579,10 +3576,10 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>444.91703647500003</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>270.96033459</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3628,7 +3625,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3640,10 +3637,10 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>12.265067756451614</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12.162871361764708</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3689,7 +3686,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3701,10 +3698,10 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>56.773512744497907</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30.896724855277501</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3750,7 +3747,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3762,10 +3759,10 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>16.968055363092642</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>16.869490869290352</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3815,7 +3812,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3827,10 +3824,10 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>3.532178303501099</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.4628647767215899</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3880,7 +3877,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3892,10 +3889,10 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>6.3586679999999998</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.3586679999999998</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3941,7 +3938,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3956,7 +3953,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-19.350000000000001</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4273,7 +4270,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4329,7 +4326,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4439,7 +4436,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4451,10 +4448,10 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>517345.39124999999</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>315070.15649999998</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4498,7 +4495,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4510,10 +4507,10 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>14261.706693548385</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>14142.873676470586</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4612,7 +4609,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4624,10 +4621,10 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>7393.7999999999993</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7393.7999999999993</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4671,7 +4668,7 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4686,7 +4683,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-22500</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5783,7 +5780,7 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>330000</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -5792,10 +5789,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>165000</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>22345.391249999997</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -5818,7 +5815,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5882,7 +5879,7 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>300000</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -5891,10 +5888,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6132</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8938.1564999999991</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -6168,10 +6165,10 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6227,10 +6224,10 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6286,10 +6283,10 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6301,13 +6298,13 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>444.91703647500003</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>270.96033459</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>270.96033459</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6351,10 +6348,10 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6366,13 +6363,13 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>12.265067756451614</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12.162871361764708</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12.162871361764708</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6514,10 +6511,10 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6529,13 +6526,13 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>6.3586679999999998</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.3586679999999998</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.3586679999999998</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6579,10 +6576,10 @@
                   <c:v>Min. BCA 2022 Compliance</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6597,10 +6594,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-19.350000000000001</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-19.350000000000001</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6995,7 +6992,7 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1346.7741935483871</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -7004,13 +7001,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8613</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2936.25</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1365.6824999999999</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7030,7 +7027,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7078,7 +7075,7 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1227.9411764705883</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -7087,13 +7084,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8613</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2936.25</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1365.6824999999999</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7442,19 +7439,19 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>4868.5613308115244</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>218748.6</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6570</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7391.25</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -7480,7 +7477,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>123 Address</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7531,19 +7528,19 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>4438.982389857566</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>81249.48000000001</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6570</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7391.25</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -14869,8 +14866,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="16976270" y="5674179"/>
-              <a:ext cx="5414283" cy="2897505"/>
+              <a:off x="17505860" y="5397954"/>
+              <a:ext cx="5591448" cy="2745105"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -14889,7 +14886,7 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="en-AU" sz="1100"/>
+                <a:rPr lang="en-CA" sz="1100"/>
                 <a:t>This chart isn't available in your version of Excel.
 Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
               </a:r>
@@ -15791,35 +15788,35 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="B1:V33"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="5.7109375" style="21" customWidth="1"/>
-    <col min="3" max="3" width="2.42578125" style="21" customWidth="1"/>
-    <col min="4" max="5" width="5.7109375" style="21" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" style="21" customWidth="1"/>
-    <col min="7" max="7" width="5.7109375" style="21" customWidth="1"/>
-    <col min="8" max="8" width="4.28515625" style="21" customWidth="1"/>
-    <col min="9" max="9" width="4.85546875" style="21" customWidth="1"/>
-    <col min="10" max="10" width="5.7109375" style="21" customWidth="1"/>
-    <col min="11" max="11" width="3.140625" style="21" customWidth="1"/>
-    <col min="12" max="12" width="5.28515625" style="21" customWidth="1"/>
-    <col min="13" max="13" width="5.5703125" style="21" customWidth="1"/>
-    <col min="14" max="15" width="5.7109375" style="21" customWidth="1"/>
-    <col min="16" max="16" width="5.140625" style="21" customWidth="1"/>
-    <col min="17" max="17" width="5.85546875" style="21" customWidth="1"/>
-    <col min="18" max="18" width="5.5703125" style="21" customWidth="1"/>
-    <col min="19" max="19" width="6.42578125" style="21" customWidth="1"/>
-    <col min="20" max="20" width="6.140625" style="21" customWidth="1"/>
-    <col min="21" max="21" width="3.140625" style="21" customWidth="1"/>
-    <col min="22" max="37" width="5.7109375" style="21" customWidth="1"/>
-    <col min="38" max="16384" width="8.85546875" style="21"/>
+    <col min="1" max="2" width="5.6640625" style="21" customWidth="1"/>
+    <col min="3" max="3" width="2.44140625" style="21" customWidth="1"/>
+    <col min="4" max="5" width="5.6640625" style="21" customWidth="1"/>
+    <col min="6" max="6" width="4.5546875" style="21" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" style="21" customWidth="1"/>
+    <col min="8" max="8" width="4.33203125" style="21" customWidth="1"/>
+    <col min="9" max="9" width="4.88671875" style="21" customWidth="1"/>
+    <col min="10" max="10" width="5.6640625" style="21" customWidth="1"/>
+    <col min="11" max="11" width="3.109375" style="21" customWidth="1"/>
+    <col min="12" max="12" width="5.33203125" style="21" customWidth="1"/>
+    <col min="13" max="13" width="5.5546875" style="21" customWidth="1"/>
+    <col min="14" max="15" width="5.6640625" style="21" customWidth="1"/>
+    <col min="16" max="16" width="5.109375" style="21" customWidth="1"/>
+    <col min="17" max="17" width="5.88671875" style="21" customWidth="1"/>
+    <col min="18" max="18" width="5.5546875" style="21" customWidth="1"/>
+    <col min="19" max="19" width="6.44140625" style="21" customWidth="1"/>
+    <col min="20" max="20" width="6.109375" style="21" customWidth="1"/>
+    <col min="21" max="21" width="3.109375" style="21" customWidth="1"/>
+    <col min="22" max="37" width="5.6640625" style="21" customWidth="1"/>
+    <col min="38" max="16384" width="8.88671875" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:22" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="102"/>
       <c r="V1" s="102"/>
     </row>
-    <row r="2" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C2" s="24"/>
       <c r="D2" s="24"/>
       <c r="E2" s="24"/>
@@ -15840,7 +15837,7 @@
       <c r="T2" s="24"/>
       <c r="U2" s="24"/>
     </row>
-    <row r="3" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="24"/>
       <c r="D3" s="24"/>
       <c r="E3" s="24"/>
@@ -15861,7 +15858,7 @@
       <c r="T3" s="24"/>
       <c r="U3" s="24"/>
     </row>
-    <row r="4" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="24"/>
       <c r="D4" s="24"/>
       <c r="E4" s="24"/>
@@ -15882,7 +15879,7 @@
       <c r="T4" s="24"/>
       <c r="U4" s="24"/>
     </row>
-    <row r="5" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="24"/>
       <c r="D5" s="24"/>
       <c r="E5" s="24"/>
@@ -15903,7 +15900,7 @@
       <c r="T5" s="24"/>
       <c r="U5" s="24"/>
     </row>
-    <row r="6" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C6" s="24"/>
       <c r="D6" s="24"/>
       <c r="E6" s="24"/>
@@ -15924,7 +15921,7 @@
       <c r="T6" s="24"/>
       <c r="U6" s="24"/>
     </row>
-    <row r="7" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="24"/>
       <c r="D7" s="24"/>
       <c r="E7" s="24"/>
@@ -15945,7 +15942,7 @@
       <c r="T7" s="24"/>
       <c r="U7" s="24"/>
     </row>
-    <row r="8" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="24"/>
       <c r="D8" s="24"/>
       <c r="E8" s="24"/>
@@ -15966,35 +15963,35 @@
       <c r="T8" s="24"/>
       <c r="U8" s="24"/>
     </row>
-    <row r="9" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="120">
+    <row r="9" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="121">
         <f>'Totals Non-Residential'!F98</f>
-        <v>347911.77370870829</v>
-      </c>
-      <c r="D9" s="120"/>
-      <c r="E9" s="120"/>
-      <c r="F9" s="120"/>
-      <c r="G9" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="118" t="s">
         <v>52</v>
       </c>
-      <c r="H9" s="117"/>
-      <c r="I9" s="117"/>
-      <c r="J9" s="118" t="s">
-        <v>240</v>
-      </c>
-      <c r="K9" s="118"/>
-      <c r="L9" s="118"/>
-      <c r="M9" s="118"/>
-      <c r="N9" s="118"/>
-      <c r="O9" s="118"/>
-      <c r="P9" s="118"/>
-      <c r="Q9" s="118"/>
-      <c r="R9" s="118"/>
-      <c r="S9" s="118"/>
-      <c r="T9" s="118"/>
+      <c r="H9" s="119"/>
+      <c r="I9" s="119"/>
+      <c r="J9" s="117" t="s">
+        <v>239</v>
+      </c>
+      <c r="K9" s="117"/>
+      <c r="L9" s="117"/>
+      <c r="M9" s="117"/>
+      <c r="N9" s="117"/>
+      <c r="O9" s="117"/>
+      <c r="P9" s="117"/>
+      <c r="Q9" s="117"/>
+      <c r="R9" s="117"/>
+      <c r="S9" s="117"/>
+      <c r="T9" s="117"/>
       <c r="U9" s="24"/>
     </row>
-    <row r="10" spans="2:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="24"/>
       <c r="D10" s="24"/>
       <c r="E10" s="24"/>
@@ -16015,7 +16012,7 @@
       <c r="T10" s="24"/>
       <c r="U10" s="24"/>
     </row>
-    <row r="11" spans="2:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="24"/>
       <c r="D11" s="24"/>
       <c r="E11" s="96"/>
@@ -16036,7 +16033,7 @@
       <c r="T11" s="24"/>
       <c r="U11" s="24"/>
     </row>
-    <row r="12" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="24"/>
       <c r="D12" s="24"/>
       <c r="E12" s="24"/>
@@ -16057,7 +16054,7 @@
       <c r="T12" s="24"/>
       <c r="U12" s="24"/>
     </row>
-    <row r="13" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="24"/>
       <c r="D13" s="24"/>
       <c r="E13" s="24"/>
@@ -16078,7 +16075,7 @@
       <c r="T13" s="24"/>
       <c r="U13" s="24"/>
     </row>
-    <row r="14" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C14" s="24"/>
       <c r="D14" s="24"/>
       <c r="E14" s="24"/>
@@ -16099,13 +16096,13 @@
       <c r="T14" s="24"/>
       <c r="U14" s="24"/>
     </row>
-    <row r="15" spans="2:22" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:22" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C15" s="24"/>
-      <c r="D15" s="119">
+      <c r="D15" s="120" t="e">
         <f>'Totals Non-Residential'!K79</f>
-        <v>0.40578341857449129</v>
-      </c>
-      <c r="E15" s="119"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E15" s="120"/>
       <c r="F15" s="94" t="s">
         <v>198</v>
       </c>
@@ -16114,20 +16111,20 @@
       <c r="I15" s="99"/>
       <c r="J15" s="99"/>
       <c r="K15" s="99"/>
-      <c r="L15" s="118" t="s">
+      <c r="L15" s="117" t="s">
         <v>203</v>
       </c>
-      <c r="M15" s="118"/>
-      <c r="N15" s="118"/>
-      <c r="O15" s="118"/>
-      <c r="P15" s="118"/>
-      <c r="Q15" s="118"/>
-      <c r="R15" s="118"/>
-      <c r="S15" s="118"/>
-      <c r="T15" s="118"/>
+      <c r="M15" s="117"/>
+      <c r="N15" s="117"/>
+      <c r="O15" s="117"/>
+      <c r="P15" s="117"/>
+      <c r="Q15" s="117"/>
+      <c r="R15" s="117"/>
+      <c r="S15" s="117"/>
+      <c r="T15" s="117"/>
       <c r="U15" s="24"/>
     </row>
-    <row r="16" spans="2:22" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:22" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="24"/>
       <c r="D16" s="24"/>
       <c r="E16" s="24"/>
@@ -16148,7 +16145,7 @@
       <c r="T16" s="24"/>
       <c r="U16" s="24"/>
     </row>
-    <row r="17" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C17" s="24"/>
       <c r="D17" s="24"/>
       <c r="E17" s="24"/>
@@ -16169,7 +16166,7 @@
       <c r="T17" s="24"/>
       <c r="U17" s="24"/>
     </row>
-    <row r="18" spans="2:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:22" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C18" s="24"/>
       <c r="D18" s="24"/>
       <c r="E18" s="24"/>
@@ -16190,7 +16187,7 @@
       <c r="T18" s="24"/>
       <c r="U18" s="24"/>
     </row>
-    <row r="19" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C19" s="24"/>
       <c r="D19" s="24"/>
       <c r="E19" s="24"/>
@@ -16211,7 +16208,7 @@
       <c r="T19" s="24"/>
       <c r="U19" s="24"/>
     </row>
-    <row r="20" spans="2:22" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:22" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C20" s="24"/>
       <c r="D20" s="24"/>
       <c r="E20" s="24"/>
@@ -16232,7 +16229,7 @@
       <c r="T20" s="24"/>
       <c r="U20" s="24"/>
     </row>
-    <row r="21" spans="2:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C21" s="24"/>
       <c r="D21" s="24"/>
       <c r="E21" s="24"/>
@@ -16253,7 +16250,7 @@
       <c r="T21" s="24"/>
       <c r="U21" s="24"/>
     </row>
-    <row r="22" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C22" s="24"/>
       <c r="D22" s="24"/>
       <c r="E22" s="24"/>
@@ -16274,7 +16271,7 @@
       <c r="T22" s="100"/>
       <c r="U22" s="24"/>
     </row>
-    <row r="23" spans="2:22" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:22" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C23" s="24"/>
       <c r="D23" s="76"/>
       <c r="E23" s="76"/>
@@ -16295,33 +16292,33 @@
       <c r="T23" s="100"/>
       <c r="U23" s="24"/>
     </row>
-    <row r="24" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C24" s="24"/>
-      <c r="D24" s="121">
+      <c r="D24" s="116">
         <f>'Totals Non-Residential'!T79</f>
-        <v>104996.684676959</v>
-      </c>
-      <c r="E24" s="121"/>
-      <c r="F24" s="121"/>
-      <c r="G24" s="121"/>
-      <c r="H24" s="121"/>
-      <c r="I24" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="E24" s="116"/>
+      <c r="F24" s="116"/>
+      <c r="G24" s="116"/>
+      <c r="H24" s="116"/>
+      <c r="I24" s="117" t="s">
         <v>200</v>
       </c>
-      <c r="J24" s="118"/>
-      <c r="K24" s="118"/>
-      <c r="L24" s="118"/>
-      <c r="M24" s="118"/>
-      <c r="N24" s="118"/>
-      <c r="O24" s="118"/>
-      <c r="P24" s="118"/>
-      <c r="Q24" s="118"/>
-      <c r="R24" s="118"/>
-      <c r="S24" s="118"/>
-      <c r="T24" s="118"/>
+      <c r="J24" s="117"/>
+      <c r="K24" s="117"/>
+      <c r="L24" s="117"/>
+      <c r="M24" s="117"/>
+      <c r="N24" s="117"/>
+      <c r="O24" s="117"/>
+      <c r="P24" s="117"/>
+      <c r="Q24" s="117"/>
+      <c r="R24" s="117"/>
+      <c r="S24" s="117"/>
+      <c r="T24" s="117"/>
       <c r="U24" s="101"/>
     </row>
-    <row r="25" spans="2:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:22" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C25" s="24"/>
       <c r="D25" s="76"/>
       <c r="F25" s="76"/>
@@ -16343,11 +16340,11 @@
       </c>
       <c r="U25" s="100"/>
     </row>
-    <row r="26" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="102"/>
       <c r="V26" s="102"/>
     </row>
-    <row r="27" spans="2:22" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:22" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C27" s="74"/>
       <c r="D27" s="75"/>
       <c r="E27" s="75"/>
@@ -16365,9 +16362,9 @@
       <c r="Q27" s="75"/>
       <c r="R27" s="75"/>
     </row>
-    <row r="33" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="20:20" x14ac:dyDescent="0.3">
       <c r="T33" s="21" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -16389,38 +16386,38 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B637D33-37A1-4563-9D13-3C298E78B961}">
   <dimension ref="A2:Z98"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="32.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="13.5703125" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="13.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" customWidth="1"/>
-    <col min="13" max="13" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="13.7109375" customWidth="1"/>
-    <col min="18" max="18" width="32.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="13.7109375" customWidth="1"/>
-    <col min="23" max="23" width="32.42578125" customWidth="1"/>
-    <col min="24" max="26" width="13.7109375" customWidth="1"/>
-    <col min="28" max="29" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="13.5546875" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="13.6640625" customWidth="1"/>
+    <col min="12" max="12" width="11.44140625" customWidth="1"/>
+    <col min="13" max="13" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="13.6640625" customWidth="1"/>
+    <col min="18" max="18" width="32.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="13.6640625" customWidth="1"/>
+    <col min="23" max="23" width="32.44140625" customWidth="1"/>
+    <col min="24" max="26" width="13.6640625" customWidth="1"/>
+    <col min="28" max="29" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="H2" s="130" t="s">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="H2" s="133" t="s">
         <v>189</v>
       </c>
-      <c r="I2" s="130"/>
+      <c r="I2" s="133"/>
       <c r="J2" s="16">
         <v>0.86</v>
       </c>
       <c r="K2" t="s">
         <v>154</v>
       </c>
-      <c r="R2" s="131" t="s">
+      <c r="R2" s="134" t="s">
         <v>95</v>
       </c>
-      <c r="S2" s="131"/>
+      <c r="S2" s="134"/>
       <c r="T2" s="16">
         <v>0.28899999999999998</v>
       </c>
@@ -16437,21 +16434,21 @@
         <v>172</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="H3" s="130" t="s">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="H3" s="133" t="s">
         <v>153</v>
       </c>
-      <c r="I3" s="130"/>
+      <c r="I3" s="133"/>
       <c r="J3" s="16">
         <v>5.1529999999999999E-2</v>
       </c>
       <c r="K3" t="s">
         <v>173</v>
       </c>
-      <c r="R3" s="131" t="s">
+      <c r="R3" s="134" t="s">
         <v>96</v>
       </c>
-      <c r="S3" s="131"/>
+      <c r="S3" s="134"/>
       <c r="T3" s="16">
         <f>T2+0.05</f>
         <v>0.33899999999999997</v>
@@ -16460,11 +16457,11 @@
         <v>107</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="H4" s="130" t="s">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="H4" s="133" t="s">
         <v>180</v>
       </c>
-      <c r="I4" s="130"/>
+      <c r="I4" s="133"/>
       <c r="J4" s="16">
         <v>0</v>
       </c>
@@ -16473,7 +16470,7 @@
       </c>
       <c r="T4" s="16"/>
     </row>
-    <row r="6" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E6" s="14"/>
       <c r="F6" s="14"/>
       <c r="G6" s="14"/>
@@ -16487,30 +16484,30 @@
       <c r="O6" s="14"/>
       <c r="P6" s="14"/>
     </row>
-    <row r="7" spans="1:26" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="C7" s="132" t="s">
+    <row r="7" spans="1:26" ht="17.399999999999999" x14ac:dyDescent="0.35">
+      <c r="C7" s="130" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="133"/>
-      <c r="E7" s="133"/>
-      <c r="F7" s="133"/>
-      <c r="G7" s="133"/>
-      <c r="H7" s="133"/>
-      <c r="I7" s="133"/>
-      <c r="J7" s="133"/>
-      <c r="K7" s="133"/>
-      <c r="L7" s="133"/>
-      <c r="M7" s="133"/>
-      <c r="N7" s="133"/>
-      <c r="O7" s="133"/>
-      <c r="P7" s="133"/>
-      <c r="Q7" s="133"/>
-      <c r="R7" s="133"/>
-      <c r="S7" s="133"/>
-      <c r="T7" s="133"/>
-      <c r="U7" s="134"/>
-    </row>
-    <row r="8" spans="1:26" ht="30" x14ac:dyDescent="0.25">
+      <c r="D7" s="131"/>
+      <c r="E7" s="131"/>
+      <c r="F7" s="131"/>
+      <c r="G7" s="131"/>
+      <c r="H7" s="131"/>
+      <c r="I7" s="131"/>
+      <c r="J7" s="131"/>
+      <c r="K7" s="131"/>
+      <c r="L7" s="131"/>
+      <c r="M7" s="131"/>
+      <c r="N7" s="131"/>
+      <c r="O7" s="131"/>
+      <c r="P7" s="131"/>
+      <c r="Q7" s="131"/>
+      <c r="R7" s="131"/>
+      <c r="S7" s="131"/>
+      <c r="T7" s="131"/>
+      <c r="U7" s="132"/>
+    </row>
+    <row r="8" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C8" s="32" t="s">
         <v>109</v>
       </c>
@@ -16518,9 +16515,9 @@
       <c r="E8" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="F8" s="72" t="str">
+      <c r="F8" s="72">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
+        <v>0</v>
       </c>
       <c r="G8" s="8"/>
       <c r="H8" s="8" t="s">
@@ -16530,9 +16527,9 @@
       <c r="J8" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="K8" s="72" t="str">
+      <c r="K8" s="72">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
+        <v>0</v>
       </c>
       <c r="M8" s="72" t="s">
         <v>192</v>
@@ -16541,9 +16538,9 @@
       <c r="O8" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="P8" s="72" t="str">
+      <c r="P8" s="72">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
+        <v>0</v>
       </c>
       <c r="R8" s="8" t="s">
         <v>105</v>
@@ -16552,22 +16549,22 @@
       <c r="T8" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="U8" s="78" t="str">
+      <c r="U8" s="78">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" ht="30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C9" s="63" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E9" s="14">
         <f>'Calculations Retail'!C9</f>
-        <v>330000</v>
+        <v>0</v>
       </c>
       <c r="F9" s="14">
         <f>'Calculations Retail'!G9</f>
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="G9" s="14"/>
       <c r="H9" s="14" t="str">
@@ -16578,11 +16575,11 @@
       <c r="I9" s="14"/>
       <c r="J9" s="14">
         <f>(E9*$J$2)/1000</f>
-        <v>283.8</v>
+        <v>0</v>
       </c>
       <c r="K9" s="14">
         <f>(F9*$J$2)/1000</f>
-        <v>258</v>
+        <v>0</v>
       </c>
       <c r="L9" s="14"/>
       <c r="M9" s="14" t="str">
@@ -16593,11 +16590,11 @@
       <c r="N9" s="14"/>
       <c r="O9" s="14">
         <f>(E9*$J$2)/1000</f>
-        <v>283.8</v>
+        <v>0</v>
       </c>
       <c r="P9" s="14">
         <f>IF('Inputs Non-Residential'!D16="Whole Development",((F9*$J$4)/1000),((F9*$J$2)/1000))</f>
-        <v>258</v>
+        <v>0</v>
       </c>
       <c r="R9" t="str">
         <f>C9</f>
@@ -16606,16 +16603,16 @@
       </c>
       <c r="T9" s="33">
         <f>E9*$T$2</f>
-        <v>95370</v>
+        <v>0</v>
       </c>
       <c r="U9" s="40">
         <f>F9*$T$2</f>
-        <v>86700</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" ht="30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C10" s="63" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E10" s="14">
         <f>'Calculations Retail'!C17*0.277776</f>
@@ -16661,7 +16658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
       <c r="C11" s="19" t="s">
         <v>145</v>
       </c>
@@ -16709,17 +16706,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
       <c r="C12" s="19" t="s">
         <v>98</v>
       </c>
       <c r="E12" s="14">
         <f>'Calculations Retail'!C27</f>
-        <v>165000</v>
+        <v>0</v>
       </c>
       <c r="F12" s="14">
         <f>'Calculations Retail'!G27</f>
-        <v>6132</v>
+        <v>0</v>
       </c>
       <c r="G12" s="14"/>
       <c r="H12" s="14" t="str">
@@ -16729,11 +16726,11 @@
       <c r="I12" s="14"/>
       <c r="J12" s="14">
         <f t="shared" si="0"/>
-        <v>141.9</v>
+        <v>0</v>
       </c>
       <c r="K12" s="14">
         <f t="shared" si="0"/>
-        <v>5.2735199999999995</v>
+        <v>0</v>
       </c>
       <c r="L12" s="14"/>
       <c r="M12" s="14" t="str">
@@ -16743,11 +16740,11 @@
       <c r="N12" s="14"/>
       <c r="O12" s="14">
         <f>(E12*$J$2)/1000</f>
-        <v>141.9</v>
+        <v>0</v>
       </c>
       <c r="P12" s="14">
         <f>IF('Inputs Non-Residential'!D16="Whole Development",((F12*$J$4)/1000),((F12*$J$2)/1000))</f>
-        <v>5.2735199999999995</v>
+        <v>0</v>
       </c>
       <c r="R12" t="str">
         <f>C12</f>
@@ -16755,24 +16752,24 @@
       </c>
       <c r="T12" s="33">
         <f t="shared" si="1"/>
-        <v>47685</v>
+        <v>0</v>
       </c>
       <c r="U12" s="40">
         <f t="shared" si="1"/>
-        <v>1772.1479999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
       <c r="C13" s="19" t="s">
         <v>99</v>
       </c>
       <c r="E13" s="14">
         <f>'Calculations Retail'!C38</f>
-        <v>22345.391249999997</v>
+        <v>0</v>
       </c>
       <c r="F13" s="14">
         <f>'Calculations Retail'!G38</f>
-        <v>8938.1564999999991</v>
+        <v>0</v>
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="14" t="str">
@@ -16782,11 +16779,11 @@
       <c r="I13" s="14"/>
       <c r="J13" s="14">
         <f t="shared" si="0"/>
-        <v>19.217036474999997</v>
+        <v>0</v>
       </c>
       <c r="K13" s="14">
         <f t="shared" si="0"/>
-        <v>7.6868145899999991</v>
+        <v>0</v>
       </c>
       <c r="L13" s="14"/>
       <c r="M13" s="14" t="str">
@@ -16796,11 +16793,11 @@
       <c r="N13" s="14"/>
       <c r="O13" s="14">
         <f>(E13*$J$2)/1000</f>
-        <v>19.217036474999997</v>
+        <v>0</v>
       </c>
       <c r="P13" s="14">
         <f>IF('Inputs Non-Residential'!D16="Whole Development",((F13*$J$4)/1000),((F13*$J$2)/1000))</f>
-        <v>7.6868145899999991</v>
+        <v>0</v>
       </c>
       <c r="R13" t="str">
         <f>C13</f>
@@ -16808,14 +16805,14 @@
       </c>
       <c r="T13" s="33">
         <f t="shared" si="1"/>
-        <v>6457.8180712499989</v>
+        <v>0</v>
       </c>
       <c r="U13" s="40">
         <f t="shared" si="1"/>
-        <v>2583.1272284999995</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14"/>
       <c r="B14"/>
       <c r="C14" s="19" t="s">
@@ -16873,18 +16870,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C15" s="34" t="s">
         <v>94</v>
       </c>
       <c r="D15" s="38"/>
       <c r="E15" s="35">
         <f>SUM(E9:E14)</f>
-        <v>517345.39124999999</v>
+        <v>0</v>
       </c>
       <c r="F15" s="35">
         <f>SUM(F9:F14)</f>
-        <v>315070.15649999998</v>
+        <v>0</v>
       </c>
       <c r="G15" s="35"/>
       <c r="H15" s="35" t="str">
@@ -16894,11 +16891,11 @@
       <c r="I15" s="35"/>
       <c r="J15" s="35">
         <f>SUM(J9:J14)</f>
-        <v>444.91703647500003</v>
+        <v>0</v>
       </c>
       <c r="K15" s="35">
         <f>SUM(K9:K14)</f>
-        <v>270.96033459</v>
+        <v>0</v>
       </c>
       <c r="L15" s="35"/>
       <c r="M15" s="35" t="str">
@@ -16908,11 +16905,11 @@
       <c r="N15" s="35"/>
       <c r="O15" s="35">
         <f>SUM(O9:O14)</f>
-        <v>444.91703647500003</v>
+        <v>0</v>
       </c>
       <c r="P15" s="35">
         <f>SUM(P9:P14)</f>
-        <v>270.96033459</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="38"/>
       <c r="R15" s="38" t="str">
@@ -16922,14 +16919,14 @@
       <c r="S15" s="38"/>
       <c r="T15" s="39">
         <f>E15*$T$2</f>
-        <v>149512.81807124999</v>
+        <v>0</v>
       </c>
       <c r="U15" s="43">
         <f>F15*$T$2</f>
-        <v>91055.275228499988</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E16" s="14"/>
       <c r="F16" s="14"/>
       <c r="G16" s="14"/>
@@ -16943,30 +16940,30 @@
       <c r="O16" s="14"/>
       <c r="P16" s="14"/>
     </row>
-    <row r="17" spans="3:21" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="C17" s="132" t="s">
+    <row r="17" spans="3:21" ht="17.399999999999999" x14ac:dyDescent="0.35">
+      <c r="C17" s="130" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="133"/>
-      <c r="E17" s="133"/>
-      <c r="F17" s="133"/>
-      <c r="G17" s="133"/>
-      <c r="H17" s="133"/>
-      <c r="I17" s="133"/>
-      <c r="J17" s="133"/>
-      <c r="K17" s="133"/>
-      <c r="L17" s="133"/>
-      <c r="M17" s="133"/>
-      <c r="N17" s="133"/>
-      <c r="O17" s="133"/>
-      <c r="P17" s="133"/>
-      <c r="Q17" s="133"/>
-      <c r="R17" s="133"/>
-      <c r="S17" s="133"/>
-      <c r="T17" s="133"/>
-      <c r="U17" s="134"/>
-    </row>
-    <row r="18" spans="3:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="D17" s="131"/>
+      <c r="E17" s="131"/>
+      <c r="F17" s="131"/>
+      <c r="G17" s="131"/>
+      <c r="H17" s="131"/>
+      <c r="I17" s="131"/>
+      <c r="J17" s="131"/>
+      <c r="K17" s="131"/>
+      <c r="L17" s="131"/>
+      <c r="M17" s="131"/>
+      <c r="N17" s="131"/>
+      <c r="O17" s="131"/>
+      <c r="P17" s="131"/>
+      <c r="Q17" s="131"/>
+      <c r="R17" s="131"/>
+      <c r="S17" s="131"/>
+      <c r="T17" s="131"/>
+      <c r="U17" s="132"/>
+    </row>
+    <row r="18" spans="3:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C18" s="32" t="s">
         <v>109</v>
       </c>
@@ -16974,9 +16971,9 @@
       <c r="E18" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="F18" s="72" t="str">
+      <c r="F18" s="72">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
+        <v>0</v>
       </c>
       <c r="G18" s="8"/>
       <c r="H18" s="8" t="s">
@@ -16986,9 +16983,9 @@
       <c r="J18" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="K18" s="72" t="str">
+      <c r="K18" s="72">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
+        <v>0</v>
       </c>
       <c r="M18" s="72" t="s">
         <v>192</v>
@@ -16997,9 +16994,9 @@
       <c r="O18" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="P18" s="72" t="str">
+      <c r="P18" s="72">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
+        <v>0</v>
       </c>
       <c r="R18" s="8" t="s">
         <v>105</v>
@@ -17008,22 +17005,22 @@
       <c r="T18" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="U18" s="78" t="str">
+      <c r="U18" s="78">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
-      </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C19" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E19" s="14">
         <f>'Calculations Office'!C9</f>
-        <v>1346.7741935483871</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
         <f>'Calculations Office'!G9</f>
-        <v>1227.9411764705883</v>
+        <v>0</v>
       </c>
       <c r="G19" s="14"/>
       <c r="H19" s="14" t="str">
@@ -17033,11 +17030,11 @@
       <c r="I19" s="14"/>
       <c r="J19" s="14">
         <f>(E19*$J$2)/1000</f>
-        <v>1.1582258064516129</v>
+        <v>0</v>
       </c>
       <c r="K19" s="14">
         <f>(F19*$J$2)/1000</f>
-        <v>1.0560294117647058</v>
+        <v>0</v>
       </c>
       <c r="L19" s="14"/>
       <c r="M19" s="14" t="str">
@@ -17047,11 +17044,11 @@
       <c r="N19" s="14"/>
       <c r="O19" s="14">
         <f t="shared" ref="O19:O24" si="2">(E19*$J$2)/1000</f>
-        <v>1.1582258064516129</v>
+        <v>0</v>
       </c>
       <c r="P19" s="14">
         <f>IF('Inputs Non-Residential'!D16="Whole Development",((F19*$J$4)/1000),((F19*$J$2)/1000))</f>
-        <v>1.0560294117647058</v>
+        <v>0</v>
       </c>
       <c r="R19" t="str">
         <f>C19</f>
@@ -17059,14 +17056,14 @@
       </c>
       <c r="T19" s="33">
         <f>E19*$T$2</f>
-        <v>389.21774193548384</v>
+        <v>0</v>
       </c>
       <c r="U19" s="40">
         <f>F19*$T$2</f>
-        <v>354.875</v>
-      </c>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C20" s="19" t="s">
         <v>171</v>
       </c>
@@ -17119,7 +17116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C21" s="19" t="s">
         <v>145</v>
       </c>
@@ -17167,17 +17164,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C22" s="19" t="s">
         <v>97</v>
       </c>
       <c r="E22" s="14">
         <f>'Calculations Office'!C27</f>
-        <v>8613</v>
+        <v>0</v>
       </c>
       <c r="F22" s="14">
         <f>'Calculations Office'!G27</f>
-        <v>8613</v>
+        <v>0</v>
       </c>
       <c r="G22" s="14"/>
       <c r="H22" s="14" t="str">
@@ -17187,11 +17184,11 @@
       <c r="I22" s="14"/>
       <c r="J22" s="14">
         <f t="shared" si="3"/>
-        <v>7.4071800000000003</v>
+        <v>0</v>
       </c>
       <c r="K22" s="14">
         <f t="shared" si="3"/>
-        <v>7.4071800000000003</v>
+        <v>0</v>
       </c>
       <c r="L22" s="14"/>
       <c r="M22" s="14" t="str">
@@ -17201,11 +17198,11 @@
       <c r="N22" s="14"/>
       <c r="O22" s="14">
         <f t="shared" si="2"/>
-        <v>7.4071800000000003</v>
+        <v>0</v>
       </c>
       <c r="P22" s="14">
         <f>IF('Inputs Non-Residential'!D16="Whole Development",((F22*$J$4)/1000),((F22*$J$2)/1000))</f>
-        <v>7.4071800000000003</v>
+        <v>0</v>
       </c>
       <c r="R22" t="str">
         <f>C22</f>
@@ -17213,24 +17210,24 @@
       </c>
       <c r="T22" s="33">
         <f t="shared" si="4"/>
-        <v>2489.1569999999997</v>
+        <v>0</v>
       </c>
       <c r="U22" s="40">
         <f t="shared" si="4"/>
-        <v>2489.1569999999997</v>
-      </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C23" s="19" t="s">
         <v>98</v>
       </c>
       <c r="E23" s="14">
         <f>'Calculations Office'!C33</f>
-        <v>2936.25</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
         <f>'Calculations Office'!G33</f>
-        <v>2936.25</v>
+        <v>0</v>
       </c>
       <c r="G23" s="14"/>
       <c r="H23" s="14" t="str">
@@ -17240,11 +17237,11 @@
       <c r="I23" s="14"/>
       <c r="J23" s="14">
         <f t="shared" si="3"/>
-        <v>2.5251750000000004</v>
+        <v>0</v>
       </c>
       <c r="K23" s="14">
         <f t="shared" si="3"/>
-        <v>2.5251750000000004</v>
+        <v>0</v>
       </c>
       <c r="L23" s="14"/>
       <c r="M23" s="14" t="str">
@@ -17254,11 +17251,11 @@
       <c r="N23" s="14"/>
       <c r="O23" s="14">
         <f t="shared" si="2"/>
-        <v>2.5251750000000004</v>
+        <v>0</v>
       </c>
       <c r="P23" s="14">
         <f>IF('Inputs Non-Residential'!D16="Whole Development",((F23*$J$4)/1000),((F23*$J$2)/1000))</f>
-        <v>2.5251750000000004</v>
+        <v>0</v>
       </c>
       <c r="R23" t="str">
         <f>C23</f>
@@ -17266,24 +17263,24 @@
       </c>
       <c r="T23" s="33">
         <f t="shared" si="4"/>
-        <v>848.57624999999996</v>
+        <v>0</v>
       </c>
       <c r="U23" s="40">
         <f t="shared" si="4"/>
-        <v>848.57624999999996</v>
-      </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C24" s="19" t="s">
         <v>99</v>
       </c>
       <c r="E24" s="14">
         <f>'Calculations Office'!C44</f>
-        <v>1365.6824999999999</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
         <f>'Calculations Office'!G44</f>
-        <v>1365.6824999999999</v>
+        <v>0</v>
       </c>
       <c r="G24" s="14"/>
       <c r="H24" s="14" t="str">
@@ -17293,11 +17290,11 @@
       <c r="I24" s="14"/>
       <c r="J24" s="14">
         <f t="shared" si="3"/>
-        <v>1.1744869499999999</v>
+        <v>0</v>
       </c>
       <c r="K24" s="14">
         <f t="shared" si="3"/>
-        <v>1.1744869499999999</v>
+        <v>0</v>
       </c>
       <c r="L24" s="14"/>
       <c r="M24" s="14" t="str">
@@ -17307,11 +17304,11 @@
       <c r="N24" s="14"/>
       <c r="O24" s="14">
         <f t="shared" si="2"/>
-        <v>1.1744869499999999</v>
+        <v>0</v>
       </c>
       <c r="P24" s="14">
         <f>IF('Inputs Non-Residential'!D16="Whole Development",((F24*$J$4)/1000),((F24*$J$2)/1000))</f>
-        <v>1.1744869499999999</v>
+        <v>0</v>
       </c>
       <c r="R24" t="str">
         <f>C24</f>
@@ -17319,25 +17316,25 @@
       </c>
       <c r="T24" s="33">
         <f t="shared" si="4"/>
-        <v>394.68224249999992</v>
+        <v>0</v>
       </c>
       <c r="U24" s="40">
         <f t="shared" si="4"/>
-        <v>394.68224249999992</v>
-      </c>
-    </row>
-    <row r="25" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C25" s="34" t="s">
         <v>94</v>
       </c>
       <c r="D25" s="38"/>
       <c r="E25" s="35">
         <f>SUM(E19:E24)</f>
-        <v>14261.706693548385</v>
+        <v>0</v>
       </c>
       <c r="F25" s="35">
         <f>SUM(F19:F24)</f>
-        <v>14142.873676470586</v>
+        <v>0</v>
       </c>
       <c r="G25" s="35"/>
       <c r="H25" s="35" t="str">
@@ -17347,11 +17344,11 @@
       <c r="I25" s="35"/>
       <c r="J25" s="35">
         <f>SUM(J19:J24)</f>
-        <v>12.265067756451614</v>
+        <v>0</v>
       </c>
       <c r="K25" s="35">
         <f>SUM(K19:K24)</f>
-        <v>12.162871361764708</v>
+        <v>0</v>
       </c>
       <c r="L25" s="35"/>
       <c r="M25" s="35" t="str">
@@ -17361,11 +17358,11 @@
       <c r="N25" s="35"/>
       <c r="O25" s="35">
         <f>SUM(O19:O24)</f>
-        <v>12.265067756451614</v>
+        <v>0</v>
       </c>
       <c r="P25" s="35">
         <f>SUM(P19:P24)</f>
-        <v>12.162871361764708</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="38"/>
       <c r="R25" s="38" t="str">
@@ -17375,14 +17372,14 @@
       <c r="S25" s="38"/>
       <c r="T25" s="39">
         <f>E25</f>
-        <v>14261.706693548385</v>
+        <v>0</v>
       </c>
       <c r="U25" s="43">
         <f>F25</f>
-        <v>14142.873676470586</v>
-      </c>
-    </row>
-    <row r="26" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="17"/>
@@ -17403,30 +17400,30 @@
       <c r="T26" s="77"/>
       <c r="U26" s="77"/>
     </row>
-    <row r="27" spans="3:21" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="C27" s="132" t="s">
+    <row r="27" spans="3:21" ht="17.399999999999999" x14ac:dyDescent="0.35">
+      <c r="C27" s="130" t="s">
         <v>230</v>
       </c>
-      <c r="D27" s="133"/>
-      <c r="E27" s="133"/>
-      <c r="F27" s="133"/>
-      <c r="G27" s="133"/>
-      <c r="H27" s="133"/>
-      <c r="I27" s="133"/>
-      <c r="J27" s="133"/>
-      <c r="K27" s="133"/>
-      <c r="L27" s="133"/>
-      <c r="M27" s="133"/>
-      <c r="N27" s="133"/>
-      <c r="O27" s="133"/>
-      <c r="P27" s="133"/>
-      <c r="Q27" s="133"/>
-      <c r="R27" s="133"/>
-      <c r="S27" s="133"/>
-      <c r="T27" s="133"/>
-      <c r="U27" s="134"/>
-    </row>
-    <row r="28" spans="3:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="D27" s="131"/>
+      <c r="E27" s="131"/>
+      <c r="F27" s="131"/>
+      <c r="G27" s="131"/>
+      <c r="H27" s="131"/>
+      <c r="I27" s="131"/>
+      <c r="J27" s="131"/>
+      <c r="K27" s="131"/>
+      <c r="L27" s="131"/>
+      <c r="M27" s="131"/>
+      <c r="N27" s="131"/>
+      <c r="O27" s="131"/>
+      <c r="P27" s="131"/>
+      <c r="Q27" s="131"/>
+      <c r="R27" s="131"/>
+      <c r="S27" s="131"/>
+      <c r="T27" s="131"/>
+      <c r="U27" s="132"/>
+    </row>
+    <row r="28" spans="3:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C28" s="32" t="s">
         <v>109</v>
       </c>
@@ -17434,9 +17431,9 @@
       <c r="E28" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="F28" s="72" t="str">
+      <c r="F28" s="72">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
+        <v>0</v>
       </c>
       <c r="G28" s="8"/>
       <c r="H28" s="8" t="s">
@@ -17446,9 +17443,9 @@
       <c r="J28" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="K28" s="72" t="str">
+      <c r="K28" s="72">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
+        <v>0</v>
       </c>
       <c r="M28" s="72" t="s">
         <v>192</v>
@@ -17457,9 +17454,9 @@
       <c r="O28" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="P28" s="72" t="str">
+      <c r="P28" s="72">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
+        <v>0</v>
       </c>
       <c r="R28" s="8" t="s">
         <v>105</v>
@@ -17468,22 +17465,22 @@
       <c r="T28" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="U28" s="78" t="str">
+      <c r="U28" s="78">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
-      </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C29" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E29" s="14">
         <f>'Calculations Student Accom'!C9</f>
-        <v>4868.5613308115244</v>
+        <v>0</v>
       </c>
       <c r="F29" s="14">
         <f>'Calculations Student Accom'!G9</f>
-        <v>4438.982389857566</v>
+        <v>0</v>
       </c>
       <c r="G29" s="14"/>
       <c r="H29" s="14" t="str">
@@ -17493,11 +17490,11 @@
       <c r="I29" s="14"/>
       <c r="J29" s="14">
         <f>(E29*$J$2)/1000</f>
-        <v>4.1869627444979107</v>
+        <v>0</v>
       </c>
       <c r="K29" s="14">
         <f>(F29*$J$2)/1000</f>
-        <v>3.8175248552775063</v>
+        <v>0</v>
       </c>
       <c r="L29" s="14"/>
       <c r="M29" s="14" t="str">
@@ -17507,11 +17504,11 @@
       <c r="N29" s="14"/>
       <c r="O29" s="14">
         <f>(E29*$J$2)/1000</f>
-        <v>4.1869627444979107</v>
+        <v>0</v>
       </c>
       <c r="P29" s="14">
         <f>IF('Inputs Non-Residential'!$D$16="Whole Development",((F29*$J$4)/1000),((F29*$J$2)/1000))</f>
-        <v>3.8175248552775063</v>
+        <v>0</v>
       </c>
       <c r="R29" t="str">
         <f>C29</f>
@@ -17519,24 +17516,24 @@
       </c>
       <c r="T29" s="33">
         <f>E29*$T$2</f>
-        <v>1407.0142246045305</v>
+        <v>0</v>
       </c>
       <c r="U29" s="40">
         <f>F29*$T$2</f>
-        <v>1282.8659106688365</v>
-      </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C30" s="19" t="s">
         <v>171</v>
       </c>
       <c r="E30" s="14">
         <f>'Calculations Student Accom'!C17*0.277776</f>
-        <v>218748.6</v>
+        <v>0</v>
       </c>
       <c r="F30" s="14">
         <f>'Calculations Student Accom'!G17*0.277776</f>
-        <v>81249.48000000001</v>
+        <v>0</v>
       </c>
       <c r="G30" s="14"/>
       <c r="H30" t="s">
@@ -17544,11 +17541,11 @@
       </c>
       <c r="J30" s="14">
         <f>('Calculations Student Accom'!C17*J3)/1000</f>
-        <v>40.579875000000001</v>
+        <v>0</v>
       </c>
       <c r="K30" s="14">
         <f>('Calculations Student Accom'!G17*J3)/1000</f>
-        <v>15.072524999999999</v>
+        <v>0</v>
       </c>
       <c r="L30" s="14"/>
       <c r="M30" t="s">
@@ -17556,25 +17553,25 @@
       </c>
       <c r="O30" s="14">
         <f>J30</f>
-        <v>40.579875000000001</v>
+        <v>0</v>
       </c>
       <c r="P30" s="14">
         <f>K30</f>
-        <v>15.072524999999999</v>
+        <v>0</v>
       </c>
       <c r="R30" t="s">
         <v>171</v>
       </c>
       <c r="T30" s="104">
         <f>'Calculations Student Accom'!C17*$Y$2</f>
-        <v>27562.500000000004</v>
+        <v>0</v>
       </c>
       <c r="U30" s="40">
         <f>'Calculations Student Accom'!G17*$Y$2</f>
-        <v>10237.500000000002</v>
-      </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C31" s="19" t="s">
         <v>145</v>
       </c>
@@ -17622,17 +17619,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C32" s="19" t="s">
         <v>97</v>
       </c>
       <c r="E32" s="14">
         <f>'Calculations Student Accom'!C27</f>
-        <v>6570</v>
+        <v>0</v>
       </c>
       <c r="F32" s="14">
         <f>'Calculations Student Accom'!G27</f>
-        <v>6570</v>
+        <v>0</v>
       </c>
       <c r="G32" s="14"/>
       <c r="H32" t="s">
@@ -17640,11 +17637,11 @@
       </c>
       <c r="J32" s="14">
         <f t="shared" si="5"/>
-        <v>5.6501999999999999</v>
+        <v>0</v>
       </c>
       <c r="K32" s="14">
         <f t="shared" si="5"/>
-        <v>5.6501999999999999</v>
+        <v>0</v>
       </c>
       <c r="L32" s="14"/>
       <c r="M32" t="s">
@@ -17653,31 +17650,31 @@
       <c r="O32" s="14"/>
       <c r="P32" s="14">
         <f>IF('Inputs Non-Residential'!$D$16="Whole Development",((F32*$J$4)/1000),((F32*$J$2)/1000))</f>
-        <v>5.6501999999999999</v>
+        <v>0</v>
       </c>
       <c r="R32" t="s">
         <v>97</v>
       </c>
       <c r="T32" s="33">
         <f t="shared" si="6"/>
-        <v>1898.7299999999998</v>
+        <v>0</v>
       </c>
       <c r="U32" s="40">
         <f>F32*$T$2</f>
-        <v>1898.7299999999998</v>
-      </c>
-    </row>
-    <row r="33" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C33" s="19" t="s">
         <v>98</v>
       </c>
       <c r="E33" s="14">
         <f>'Calculations Student Accom'!C33</f>
-        <v>7391.25</v>
+        <v>0</v>
       </c>
       <c r="F33" s="14">
         <f>'Calculations Student Accom'!G33</f>
-        <v>7391.25</v>
+        <v>0</v>
       </c>
       <c r="G33" s="14"/>
       <c r="H33" s="14" t="str">
@@ -17687,11 +17684,11 @@
       <c r="I33" s="14"/>
       <c r="J33" s="14">
         <f t="shared" si="5"/>
-        <v>6.3564749999999997</v>
+        <v>0</v>
       </c>
       <c r="K33" s="14">
         <f t="shared" si="5"/>
-        <v>6.3564749999999997</v>
+        <v>0</v>
       </c>
       <c r="L33" s="14"/>
       <c r="M33" s="14" t="str">
@@ -17701,11 +17698,11 @@
       <c r="N33" s="14"/>
       <c r="O33" s="14">
         <f>(E33*$J$2)/1000</f>
-        <v>6.3564749999999997</v>
+        <v>0</v>
       </c>
       <c r="P33" s="14">
         <f>IF('Inputs Non-Residential'!$D$16="Whole Development",((F33*$J$4)/1000),((F33*$J$2)/1000))</f>
-        <v>6.3564749999999997</v>
+        <v>0</v>
       </c>
       <c r="R33" t="str">
         <f>C33</f>
@@ -17713,14 +17710,14 @@
       </c>
       <c r="T33" s="33">
         <f t="shared" si="6"/>
-        <v>2136.07125</v>
+        <v>0</v>
       </c>
       <c r="U33" s="40">
         <f t="shared" ref="U33:U34" si="7">F33*$T$2</f>
-        <v>2136.07125</v>
-      </c>
-    </row>
-    <row r="34" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C34" s="19" t="s">
         <v>99</v>
       </c>
@@ -17773,7 +17770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="3:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C35" s="19" t="s">
         <v>28</v>
       </c>
@@ -17826,18 +17823,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C36" s="34" t="s">
         <v>94</v>
       </c>
       <c r="D36" s="38"/>
       <c r="E36" s="35">
         <f>SUM(E29:E35)</f>
-        <v>237578.41133081153</v>
+        <v>0</v>
       </c>
       <c r="F36" s="35">
         <f>SUM(F29:F35)</f>
-        <v>99649.712389857581</v>
+        <v>0</v>
       </c>
       <c r="G36" s="35"/>
       <c r="H36" s="35" t="str">
@@ -17847,11 +17844,11 @@
       <c r="I36" s="35"/>
       <c r="J36" s="35">
         <f>SUM(J29:J35)</f>
-        <v>56.773512744497907</v>
+        <v>0</v>
       </c>
       <c r="K36" s="35">
         <f>SUM(K29:K35)</f>
-        <v>30.896724855277501</v>
+        <v>0</v>
       </c>
       <c r="L36" s="35"/>
       <c r="M36" s="35" t="str">
@@ -17861,11 +17858,11 @@
       <c r="N36" s="35"/>
       <c r="O36" s="35">
         <f>SUM(O29:O35)</f>
-        <v>51.123312744497909</v>
+        <v>0</v>
       </c>
       <c r="P36" s="35">
         <f>SUM(P29:P35)</f>
-        <v>30.896724855277501</v>
+        <v>0</v>
       </c>
       <c r="Q36" s="38"/>
       <c r="R36" s="38" t="str">
@@ -17875,14 +17872,14 @@
       <c r="S36" s="38"/>
       <c r="T36" s="39">
         <f>E36*$T$2</f>
-        <v>68660.160874604524</v>
+        <v>0</v>
       </c>
       <c r="U36" s="43">
         <f>F36*$T$2</f>
-        <v>28798.766880668838</v>
-      </c>
-    </row>
-    <row r="37" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="17"/>
@@ -17903,30 +17900,30 @@
       <c r="T37" s="77"/>
       <c r="U37" s="77"/>
     </row>
-    <row r="38" spans="3:21" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="C38" s="132" t="s">
+    <row r="38" spans="3:21" ht="17.399999999999999" x14ac:dyDescent="0.35">
+      <c r="C38" s="130" t="s">
         <v>208</v>
       </c>
-      <c r="D38" s="133"/>
-      <c r="E38" s="133"/>
-      <c r="F38" s="133"/>
-      <c r="G38" s="133"/>
-      <c r="H38" s="133"/>
-      <c r="I38" s="133"/>
-      <c r="J38" s="133"/>
-      <c r="K38" s="133"/>
-      <c r="L38" s="133"/>
-      <c r="M38" s="133"/>
-      <c r="N38" s="133"/>
-      <c r="O38" s="133"/>
-      <c r="P38" s="133"/>
-      <c r="Q38" s="133"/>
-      <c r="R38" s="133"/>
-      <c r="S38" s="133"/>
-      <c r="T38" s="133"/>
-      <c r="U38" s="134"/>
-    </row>
-    <row r="39" spans="3:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="D38" s="131"/>
+      <c r="E38" s="131"/>
+      <c r="F38" s="131"/>
+      <c r="G38" s="131"/>
+      <c r="H38" s="131"/>
+      <c r="I38" s="131"/>
+      <c r="J38" s="131"/>
+      <c r="K38" s="131"/>
+      <c r="L38" s="131"/>
+      <c r="M38" s="131"/>
+      <c r="N38" s="131"/>
+      <c r="O38" s="131"/>
+      <c r="P38" s="131"/>
+      <c r="Q38" s="131"/>
+      <c r="R38" s="131"/>
+      <c r="S38" s="131"/>
+      <c r="T38" s="131"/>
+      <c r="U38" s="132"/>
+    </row>
+    <row r="39" spans="3:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C39" s="32" t="s">
         <v>109</v>
       </c>
@@ -17934,9 +17931,9 @@
       <c r="E39" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="F39" s="72" t="str">
+      <c r="F39" s="72">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
+        <v>0</v>
       </c>
       <c r="G39" s="8"/>
       <c r="H39" s="8" t="s">
@@ -17946,9 +17943,9 @@
       <c r="J39" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="K39" s="72" t="str">
+      <c r="K39" s="72">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
+        <v>0</v>
       </c>
       <c r="M39" s="72" t="s">
         <v>192</v>
@@ -17957,9 +17954,9 @@
       <c r="O39" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="P39" s="72" t="str">
+      <c r="P39" s="72">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
+        <v>0</v>
       </c>
       <c r="R39" s="8" t="s">
         <v>105</v>
@@ -17968,22 +17965,22 @@
       <c r="T39" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="U39" s="78" t="str">
+      <c r="U39" s="78">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
-      </c>
-    </row>
-    <row r="40" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C40" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E40" s="14">
         <f>'Calculations Educational'!C9</f>
-        <v>1298.9119338286555</v>
+        <v>0</v>
       </c>
       <c r="F40" s="14">
         <f>'Calculations Educational'!G9</f>
-        <v>1184.3020573143624</v>
+        <v>0</v>
       </c>
       <c r="G40" s="14"/>
       <c r="H40" s="14" t="str">
@@ -17993,11 +17990,11 @@
       <c r="I40" s="14"/>
       <c r="J40" s="14">
         <f>(E40*$J$2)/1000</f>
-        <v>1.1170642630926435</v>
+        <v>0</v>
       </c>
       <c r="K40" s="14">
         <f>(F40*$J$2)/1000</f>
-        <v>1.0184997692903517</v>
+        <v>0</v>
       </c>
       <c r="L40" s="14"/>
       <c r="M40" s="14" t="str">
@@ -18007,11 +18004,11 @@
       <c r="N40" s="14"/>
       <c r="O40" s="14">
         <f>(E40*$J$2)/1000</f>
-        <v>1.1170642630926435</v>
+        <v>0</v>
       </c>
       <c r="P40" s="14">
         <f>IF('Inputs Non-Residential'!$D$16="Whole Development",((F40*$J$4)/1000),((F40*$J$2)/1000))</f>
-        <v>1.0184997692903517</v>
+        <v>0</v>
       </c>
       <c r="R40" t="str">
         <f>C40</f>
@@ -18019,14 +18016,14 @@
       </c>
       <c r="T40" s="33">
         <f>E40*$T$2</f>
-        <v>375.38554887648144</v>
+        <v>0</v>
       </c>
       <c r="U40" s="40">
         <f>F40*$T$2</f>
-        <v>342.26329456385071</v>
-      </c>
-    </row>
-    <row r="41" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C41" s="19" t="s">
         <v>171</v>
       </c>
@@ -18074,7 +18071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="3:21" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C42" s="19" t="s">
         <v>145</v>
       </c>
@@ -18122,17 +18119,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="3:21" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C43" s="19" t="s">
         <v>97</v>
       </c>
       <c r="E43" s="14">
         <f>'Calculations Educational'!C27</f>
-        <v>12058.199999999999</v>
+        <v>0</v>
       </c>
       <c r="F43" s="14">
         <f>'Calculations Educational'!G27</f>
-        <v>12058.199999999999</v>
+        <v>0</v>
       </c>
       <c r="G43" s="14"/>
       <c r="H43" t="s">
@@ -18140,11 +18137,11 @@
       </c>
       <c r="J43" s="14">
         <f t="shared" si="8"/>
-        <v>10.370051999999999</v>
+        <v>0</v>
       </c>
       <c r="K43" s="14">
         <f t="shared" si="8"/>
-        <v>10.370051999999999</v>
+        <v>0</v>
       </c>
       <c r="L43" s="14"/>
       <c r="M43" t="s">
@@ -18152,25 +18149,25 @@
       </c>
       <c r="O43" s="14">
         <f>(E43*$J$2)/1000</f>
-        <v>10.370051999999999</v>
+        <v>0</v>
       </c>
       <c r="P43" s="14">
         <f>IF('Inputs Non-Residential'!$D$16="Whole Development",((F43*$J$4)/1000),((F43*$J$2)/1000))</f>
-        <v>10.370051999999999</v>
+        <v>0</v>
       </c>
       <c r="R43" t="s">
         <v>97</v>
       </c>
       <c r="T43" s="33">
         <f t="shared" si="9"/>
-        <v>3484.8197999999993</v>
+        <v>0</v>
       </c>
       <c r="U43" s="40">
         <f t="shared" si="10"/>
-        <v>3484.8197999999993</v>
-      </c>
-    </row>
-    <row r="44" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C44" s="19" t="s">
         <v>98</v>
       </c>
@@ -18223,17 +18220,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="3:21" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C45" s="19" t="s">
         <v>99</v>
       </c>
       <c r="E45" s="14">
         <f>'Calculations Educational'!C44</f>
-        <v>6373.1849999999986</v>
+        <v>0</v>
       </c>
       <c r="F45" s="14">
         <f>'Calculations Educational'!G44</f>
-        <v>6373.1849999999986</v>
+        <v>0</v>
       </c>
       <c r="G45" s="14"/>
       <c r="H45" s="14" t="str">
@@ -18243,11 +18240,11 @@
       <c r="I45" s="14"/>
       <c r="J45" s="14">
         <f t="shared" si="8"/>
-        <v>5.4809390999999987</v>
+        <v>0</v>
       </c>
       <c r="K45" s="14">
         <f t="shared" si="8"/>
-        <v>5.4809390999999987</v>
+        <v>0</v>
       </c>
       <c r="L45" s="14"/>
       <c r="M45" s="14" t="str">
@@ -18257,11 +18254,11 @@
       <c r="N45" s="14"/>
       <c r="O45" s="14">
         <f>(E45*$J$2)/1000</f>
-        <v>5.4809390999999987</v>
+        <v>0</v>
       </c>
       <c r="P45" s="14">
         <f>IF('Inputs Non-Residential'!$D$16="Whole Development",((F45*$J$4)/1000),((F45*$J$2)/1000))</f>
-        <v>5.4809390999999987</v>
+        <v>0</v>
       </c>
       <c r="R45" t="str">
         <f>C45</f>
@@ -18269,25 +18266,25 @@
       </c>
       <c r="T45" s="33">
         <f t="shared" si="9"/>
-        <v>1841.8504649999995</v>
+        <v>0</v>
       </c>
       <c r="U45" s="40">
         <f t="shared" si="10"/>
-        <v>1841.8504649999995</v>
-      </c>
-    </row>
-    <row r="46" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C46" s="34" t="s">
         <v>94</v>
       </c>
       <c r="D46" s="38"/>
       <c r="E46" s="35">
         <f>SUM(E40:E45)</f>
-        <v>19730.296933828653</v>
+        <v>0</v>
       </c>
       <c r="F46" s="35">
         <f>SUM(F40:F45)</f>
-        <v>19615.687057314361</v>
+        <v>0</v>
       </c>
       <c r="G46" s="35"/>
       <c r="H46" s="35" t="str">
@@ -18297,11 +18294,11 @@
       <c r="I46" s="35"/>
       <c r="J46" s="35">
         <f>SUM(J40:J45)</f>
-        <v>16.968055363092642</v>
+        <v>0</v>
       </c>
       <c r="K46" s="35">
         <f>SUM(K40:K45)</f>
-        <v>16.869490869290352</v>
+        <v>0</v>
       </c>
       <c r="L46" s="35"/>
       <c r="M46" s="35" t="str">
@@ -18311,11 +18308,11 @@
       <c r="N46" s="35"/>
       <c r="O46" s="35">
         <f>SUM(O40:O45)</f>
-        <v>16.968055363092642</v>
+        <v>0</v>
       </c>
       <c r="P46" s="35">
         <f>SUM(P40:P45)</f>
-        <v>16.869490869290352</v>
+        <v>0</v>
       </c>
       <c r="Q46" s="38"/>
       <c r="R46" s="38" t="str">
@@ -18325,14 +18322,14 @@
       <c r="S46" s="38"/>
       <c r="T46" s="39">
         <f>E46*$T$2</f>
-        <v>5702.05581387648</v>
+        <v>0</v>
       </c>
       <c r="U46" s="43">
         <f>F46*$T$2</f>
-        <v>5668.9335595638495</v>
-      </c>
-    </row>
-    <row r="47" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="17"/>
@@ -18353,30 +18350,30 @@
       <c r="T47" s="77"/>
       <c r="U47" s="77"/>
     </row>
-    <row r="48" spans="3:21" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="C48" s="132" t="s">
+    <row r="48" spans="3:21" ht="17.399999999999999" x14ac:dyDescent="0.35">
+      <c r="C48" s="130" t="s">
         <v>207</v>
       </c>
-      <c r="D48" s="133"/>
-      <c r="E48" s="133"/>
-      <c r="F48" s="133"/>
-      <c r="G48" s="133"/>
-      <c r="H48" s="133"/>
-      <c r="I48" s="133"/>
-      <c r="J48" s="133"/>
-      <c r="K48" s="133"/>
-      <c r="L48" s="133"/>
-      <c r="M48" s="133"/>
-      <c r="N48" s="133"/>
-      <c r="O48" s="133"/>
-      <c r="P48" s="133"/>
-      <c r="Q48" s="133"/>
-      <c r="R48" s="133"/>
-      <c r="S48" s="133"/>
-      <c r="T48" s="133"/>
-      <c r="U48" s="134"/>
-    </row>
-    <row r="49" spans="3:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="D48" s="131"/>
+      <c r="E48" s="131"/>
+      <c r="F48" s="131"/>
+      <c r="G48" s="131"/>
+      <c r="H48" s="131"/>
+      <c r="I48" s="131"/>
+      <c r="J48" s="131"/>
+      <c r="K48" s="131"/>
+      <c r="L48" s="131"/>
+      <c r="M48" s="131"/>
+      <c r="N48" s="131"/>
+      <c r="O48" s="131"/>
+      <c r="P48" s="131"/>
+      <c r="Q48" s="131"/>
+      <c r="R48" s="131"/>
+      <c r="S48" s="131"/>
+      <c r="T48" s="131"/>
+      <c r="U48" s="132"/>
+    </row>
+    <row r="49" spans="3:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C49" s="32" t="s">
         <v>109</v>
       </c>
@@ -18384,9 +18381,9 @@
       <c r="E49" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="F49" s="72" t="str">
+      <c r="F49" s="72">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
+        <v>0</v>
       </c>
       <c r="G49" s="8"/>
       <c r="H49" s="8" t="s">
@@ -18396,9 +18393,9 @@
       <c r="J49" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="K49" s="72" t="str">
+      <c r="K49" s="72">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
+        <v>0</v>
       </c>
       <c r="M49" s="72" t="s">
         <v>192</v>
@@ -18407,9 +18404,9 @@
       <c r="O49" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="P49" s="72" t="str">
+      <c r="P49" s="72">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
+        <v>0</v>
       </c>
       <c r="R49" s="8" t="s">
         <v>105</v>
@@ -18418,22 +18415,22 @@
       <c r="T49" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="U49" s="78" t="str">
+      <c r="U49" s="78">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
-      </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C50" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E50" s="14">
         <f>'Calculations Aged Care'!C9</f>
-        <v>913.43407383848762</v>
+        <v>0</v>
       </c>
       <c r="F50" s="14">
         <f>'Calculations Aged Care'!G9</f>
-        <v>832.8369496762682</v>
+        <v>0</v>
       </c>
       <c r="G50" s="14"/>
       <c r="H50" s="14" t="str">
@@ -18443,11 +18440,11 @@
       <c r="I50" s="14"/>
       <c r="J50" s="14">
         <f>(E50*$J$2)/1000</f>
-        <v>0.78555330350109931</v>
+        <v>0</v>
       </c>
       <c r="K50" s="14">
         <f>(F50*$J$2)/1000</f>
-        <v>0.71623977672159056</v>
+        <v>0</v>
       </c>
       <c r="L50" s="14"/>
       <c r="M50" s="14" t="str">
@@ -18457,11 +18454,11 @@
       <c r="N50" s="14"/>
       <c r="O50" s="14">
         <f>(E50*$J$2)/1000</f>
-        <v>0.78555330350109931</v>
+        <v>0</v>
       </c>
       <c r="P50" s="14">
         <f>IF('Inputs Non-Residential'!$D$16="Whole Development",((F50*$J$4)/1000),((F50*$J$2)/1000))</f>
-        <v>0.71623977672159056</v>
+        <v>0</v>
       </c>
       <c r="R50" t="str">
         <f>C50</f>
@@ -18469,14 +18466,14 @@
       </c>
       <c r="T50" s="33">
         <f>E50*$T$2</f>
-        <v>263.9824473393229</v>
+        <v>0</v>
       </c>
       <c r="U50" s="40">
         <f>F50*$T$2</f>
-        <v>240.68987845644151</v>
-      </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C51" s="19" t="s">
         <v>171</v>
       </c>
@@ -18524,7 +18521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C52" s="19" t="s">
         <v>145</v>
       </c>
@@ -18572,17 +18569,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C53" s="19" t="s">
         <v>97</v>
       </c>
       <c r="E53" s="14">
         <f>'Calculations Aged Care'!C27</f>
-        <v>1460</v>
+        <v>0</v>
       </c>
       <c r="F53" s="14">
         <f>'Calculations Aged Care'!G27</f>
-        <v>1460</v>
+        <v>0</v>
       </c>
       <c r="G53" s="14"/>
       <c r="H53" t="s">
@@ -18590,11 +18587,11 @@
       </c>
       <c r="J53" s="14">
         <f t="shared" si="11"/>
-        <v>1.2555999999999998</v>
+        <v>0</v>
       </c>
       <c r="K53" s="14">
         <f t="shared" si="11"/>
-        <v>1.2555999999999998</v>
+        <v>0</v>
       </c>
       <c r="L53" s="14"/>
       <c r="M53" t="s">
@@ -18602,35 +18599,35 @@
       </c>
       <c r="O53" s="14">
         <f>(E53*$J$2)/1000</f>
-        <v>1.2555999999999998</v>
+        <v>0</v>
       </c>
       <c r="P53" s="14">
         <f>IF('Inputs Non-Residential'!$D$16="Whole Development",((F53*$J$4)/1000),((F53*$J$2)/1000))</f>
-        <v>1.2555999999999998</v>
+        <v>0</v>
       </c>
       <c r="R53" t="s">
         <v>235</v>
       </c>
       <c r="T53" s="33">
         <f t="shared" si="12"/>
-        <v>421.94</v>
+        <v>0</v>
       </c>
       <c r="U53" s="40">
         <f t="shared" si="13"/>
-        <v>421.94</v>
-      </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C54" s="19" t="s">
         <v>98</v>
       </c>
       <c r="E54" s="14">
         <f>'Calculations Aged Care'!C33</f>
-        <v>1733.75</v>
+        <v>0</v>
       </c>
       <c r="F54" s="14">
         <f>'Calculations Aged Care'!G33</f>
-        <v>1733.75</v>
+        <v>0</v>
       </c>
       <c r="G54" s="14"/>
       <c r="H54" s="14" t="str">
@@ -18640,11 +18637,11 @@
       <c r="I54" s="14"/>
       <c r="J54" s="14">
         <f t="shared" si="11"/>
-        <v>1.4910249999999998</v>
+        <v>0</v>
       </c>
       <c r="K54" s="14">
         <f t="shared" si="11"/>
-        <v>1.4910249999999998</v>
+        <v>0</v>
       </c>
       <c r="L54" s="14"/>
       <c r="M54" s="14" t="str">
@@ -18654,11 +18651,11 @@
       <c r="N54" s="14"/>
       <c r="O54" s="14">
         <f>(E54*$J$2)/1000</f>
-        <v>1.4910249999999998</v>
+        <v>0</v>
       </c>
       <c r="P54" s="14">
         <f>IF('Inputs Non-Residential'!$D$16="Whole Development",((F54*$J$4)/1000),((F54*$J$2)/1000))</f>
-        <v>1.4910249999999998</v>
+        <v>0</v>
       </c>
       <c r="R54" t="str">
         <f>C54</f>
@@ -18666,14 +18663,14 @@
       </c>
       <c r="T54" s="33">
         <f t="shared" si="12"/>
-        <v>501.05374999999998</v>
+        <v>0</v>
       </c>
       <c r="U54" s="40">
         <f t="shared" si="13"/>
-        <v>501.05374999999998</v>
-      </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C55" s="19" t="s">
         <v>99</v>
       </c>
@@ -18726,7 +18723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C56" s="19" t="s">
         <v>28</v>
       </c>
@@ -18779,18 +18776,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C57" s="34" t="s">
         <v>94</v>
       </c>
       <c r="D57" s="38"/>
       <c r="E57" s="35">
         <f>SUM(E50:E56)</f>
-        <v>4107.1840738384872</v>
+        <v>0</v>
       </c>
       <c r="F57" s="35">
         <f>SUM(F50:F56)</f>
-        <v>4026.586949676268</v>
+        <v>0</v>
       </c>
       <c r="G57" s="35"/>
       <c r="H57" s="35" t="str">
@@ -18800,11 +18797,11 @@
       <c r="I57" s="35"/>
       <c r="J57" s="35">
         <f>SUM(J50:J56)</f>
-        <v>3.532178303501099</v>
+        <v>0</v>
       </c>
       <c r="K57" s="35">
         <f>SUM(K50:K56)</f>
-        <v>3.4628647767215899</v>
+        <v>0</v>
       </c>
       <c r="L57" s="35"/>
       <c r="M57" s="35" t="str">
@@ -18814,11 +18811,11 @@
       <c r="N57" s="35"/>
       <c r="O57" s="35">
         <f>SUM(O50:O56)</f>
-        <v>3.532178303501099</v>
+        <v>0</v>
       </c>
       <c r="P57" s="35">
         <f>SUM(P50:P56)</f>
-        <v>3.4628647767215899</v>
+        <v>0</v>
       </c>
       <c r="Q57" s="38"/>
       <c r="R57" s="38" t="str">
@@ -18828,14 +18825,14 @@
       <c r="S57" s="38"/>
       <c r="T57" s="39">
         <f>E57*$T$2</f>
-        <v>1186.9761973393227</v>
+        <v>0</v>
       </c>
       <c r="U57" s="43">
         <f>F57*$T$2</f>
-        <v>1163.6836284564413</v>
-      </c>
-    </row>
-    <row r="58" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="17"/>
@@ -18856,30 +18853,30 @@
       <c r="T58" s="77"/>
       <c r="U58" s="77"/>
     </row>
-    <row r="59" spans="3:21" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="C59" s="132" t="s">
+    <row r="59" spans="3:21" ht="17.399999999999999" x14ac:dyDescent="0.35">
+      <c r="C59" s="130" t="s">
         <v>234</v>
       </c>
-      <c r="D59" s="133"/>
-      <c r="E59" s="133"/>
-      <c r="F59" s="133"/>
-      <c r="G59" s="133"/>
-      <c r="H59" s="133"/>
-      <c r="I59" s="133"/>
-      <c r="J59" s="133"/>
-      <c r="K59" s="133"/>
-      <c r="L59" s="133"/>
-      <c r="M59" s="133"/>
-      <c r="N59" s="133"/>
-      <c r="O59" s="133"/>
-      <c r="P59" s="133"/>
-      <c r="Q59" s="133"/>
-      <c r="R59" s="133"/>
-      <c r="S59" s="133"/>
-      <c r="T59" s="133"/>
-      <c r="U59" s="134"/>
-    </row>
-    <row r="60" spans="3:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="D59" s="131"/>
+      <c r="E59" s="131"/>
+      <c r="F59" s="131"/>
+      <c r="G59" s="131"/>
+      <c r="H59" s="131"/>
+      <c r="I59" s="131"/>
+      <c r="J59" s="131"/>
+      <c r="K59" s="131"/>
+      <c r="L59" s="131"/>
+      <c r="M59" s="131"/>
+      <c r="N59" s="131"/>
+      <c r="O59" s="131"/>
+      <c r="P59" s="131"/>
+      <c r="Q59" s="131"/>
+      <c r="R59" s="131"/>
+      <c r="S59" s="131"/>
+      <c r="T59" s="131"/>
+      <c r="U59" s="132"/>
+    </row>
+    <row r="60" spans="3:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C60" s="32" t="s">
         <v>109</v>
       </c>
@@ -18887,9 +18884,9 @@
       <c r="E60" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="F60" s="72" t="str">
+      <c r="F60" s="72">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
+        <v>0</v>
       </c>
       <c r="G60" s="8"/>
       <c r="H60" s="8" t="s">
@@ -18899,9 +18896,9 @@
       <c r="J60" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="K60" s="8" t="str">
+      <c r="K60" s="8">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
+        <v>0</v>
       </c>
       <c r="M60" s="72" t="s">
         <v>192</v>
@@ -18910,9 +18907,9 @@
       <c r="O60" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="P60" s="72" t="str">
+      <c r="P60" s="72">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
+        <v>0</v>
       </c>
       <c r="R60" s="8" t="s">
         <v>105</v>
@@ -18921,22 +18918,22 @@
       <c r="T60" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="U60" s="78" t="str">
+      <c r="U60" s="78">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
-      </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C61" s="19" t="s">
         <v>142</v>
       </c>
       <c r="E61" s="14">
         <f>'Calculations C&amp;S'!C4</f>
-        <v>4656.2999999999993</v>
+        <v>0</v>
       </c>
       <c r="F61" s="14">
         <f>'Calculations C&amp;S'!G4</f>
-        <v>4656.2999999999993</v>
+        <v>0</v>
       </c>
       <c r="G61" s="14"/>
       <c r="H61" t="s">
@@ -18944,11 +18941,11 @@
       </c>
       <c r="J61" s="14">
         <f t="shared" ref="J61:K63" si="14">(E61*$J$2)/1000</f>
-        <v>4.0044179999999994</v>
+        <v>0</v>
       </c>
       <c r="K61" s="14">
         <f t="shared" si="14"/>
-        <v>4.0044179999999994</v>
+        <v>0</v>
       </c>
       <c r="L61" s="14"/>
       <c r="M61" t="s">
@@ -18956,35 +18953,35 @@
       </c>
       <c r="O61" s="14">
         <f>(E61*$J$2)/1000</f>
-        <v>4.0044179999999994</v>
+        <v>0</v>
       </c>
       <c r="P61" s="14">
         <f>IF('Inputs Non-Residential'!$D$16="Whole Development",F61*$J$4/1000, IF('Inputs Non-Residential'!$D$16="Base Building",F61*$J$4/1000,F61*$J$2/1000))</f>
-        <v>4.0044179999999994</v>
+        <v>0</v>
       </c>
       <c r="R61" t="s">
         <v>142</v>
       </c>
       <c r="T61" s="41">
         <f t="shared" ref="T61:U63" si="15">E61*$T$2</f>
-        <v>1345.6706999999997</v>
+        <v>0</v>
       </c>
       <c r="U61" s="42">
         <f t="shared" si="15"/>
-        <v>1345.6706999999997</v>
-      </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C62" s="19" t="s">
         <v>98</v>
       </c>
       <c r="E62" s="14">
         <f>'Calculations C&amp;S'!C10+'Calculations C&amp;S'!C16</f>
-        <v>2737.5</v>
+        <v>0</v>
       </c>
       <c r="F62" s="14">
         <f>'Calculations C&amp;S'!G10+'Calculations C&amp;S'!G16</f>
-        <v>2737.5</v>
+        <v>0</v>
       </c>
       <c r="G62" s="14"/>
       <c r="H62" t="s">
@@ -18992,11 +18989,11 @@
       </c>
       <c r="J62" s="14">
         <f t="shared" si="14"/>
-        <v>2.35425</v>
+        <v>0</v>
       </c>
       <c r="K62" s="14">
         <f t="shared" si="14"/>
-        <v>2.35425</v>
+        <v>0</v>
       </c>
       <c r="L62" s="14"/>
       <c r="M62" t="s">
@@ -19004,25 +19001,25 @@
       </c>
       <c r="O62" s="14">
         <f>(E62*$J$2)/1000</f>
-        <v>2.35425</v>
+        <v>0</v>
       </c>
       <c r="P62" s="14">
         <f>IF('Inputs Non-Residential'!$D$16="Whole Development",F62*$J$4/1000, IF('Inputs Non-Residential'!$D$16="Base Building",F62*$J$4/1000,F62*$J$2/1000))</f>
-        <v>2.35425</v>
+        <v>0</v>
       </c>
       <c r="R62" t="s">
         <v>98</v>
       </c>
       <c r="T62" s="41">
         <f t="shared" si="15"/>
-        <v>791.13749999999993</v>
+        <v>0</v>
       </c>
       <c r="U62" s="42">
         <f t="shared" si="15"/>
-        <v>791.13749999999993</v>
-      </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C63" s="19" t="s">
         <v>236</v>
       </c>
@@ -19070,18 +19067,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C64" s="34" t="s">
         <v>94</v>
       </c>
       <c r="D64" s="38"/>
       <c r="E64" s="35">
         <f>SUM(E61:E62)</f>
-        <v>7393.7999999999993</v>
+        <v>0</v>
       </c>
       <c r="F64" s="35">
         <f>SUM(F61:F62)</f>
-        <v>7393.7999999999993</v>
+        <v>0</v>
       </c>
       <c r="G64" s="35"/>
       <c r="H64" s="38" t="s">
@@ -19090,11 +19087,11 @@
       <c r="I64" s="38"/>
       <c r="J64" s="35">
         <f>SUM(J61:J62)</f>
-        <v>6.3586679999999998</v>
+        <v>0</v>
       </c>
       <c r="K64" s="35">
         <f>SUM(K61:K62)</f>
-        <v>6.3586679999999998</v>
+        <v>0</v>
       </c>
       <c r="L64" s="35"/>
       <c r="M64" s="38" t="s">
@@ -19103,11 +19100,11 @@
       <c r="N64" s="38"/>
       <c r="O64" s="35">
         <f>SUM(O61:O62)</f>
-        <v>6.3586679999999998</v>
+        <v>0</v>
       </c>
       <c r="P64" s="35">
         <f>SUM(P61:P62)</f>
-        <v>6.3586679999999998</v>
+        <v>0</v>
       </c>
       <c r="Q64" s="38"/>
       <c r="R64" s="38" t="s">
@@ -19116,14 +19113,14 @@
       <c r="S64" s="38"/>
       <c r="T64" s="39">
         <f>SUM(T61:T62)</f>
-        <v>2136.8081999999995</v>
+        <v>0</v>
       </c>
       <c r="U64" s="43">
         <f>SUM(U61:U62)</f>
-        <v>2136.8081999999995</v>
-      </c>
-    </row>
-    <row r="65" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E65" s="14"/>
       <c r="F65" s="14"/>
       <c r="G65" s="14"/>
@@ -19137,30 +19134,30 @@
       <c r="O65" s="14"/>
       <c r="P65" s="14"/>
     </row>
-    <row r="66" spans="3:21" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="C66" s="132" t="s">
+    <row r="66" spans="3:21" ht="17.399999999999999" x14ac:dyDescent="0.35">
+      <c r="C66" s="130" t="s">
         <v>100</v>
       </c>
-      <c r="D66" s="133"/>
-      <c r="E66" s="133"/>
-      <c r="F66" s="133"/>
-      <c r="G66" s="133"/>
-      <c r="H66" s="133"/>
-      <c r="I66" s="133"/>
-      <c r="J66" s="133"/>
-      <c r="K66" s="133"/>
-      <c r="L66" s="133"/>
-      <c r="M66" s="133"/>
-      <c r="N66" s="133"/>
-      <c r="O66" s="133"/>
-      <c r="P66" s="133"/>
-      <c r="Q66" s="133"/>
-      <c r="R66" s="133"/>
-      <c r="S66" s="133"/>
-      <c r="T66" s="133"/>
-      <c r="U66" s="134"/>
-    </row>
-    <row r="67" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D66" s="131"/>
+      <c r="E66" s="131"/>
+      <c r="F66" s="131"/>
+      <c r="G66" s="131"/>
+      <c r="H66" s="131"/>
+      <c r="I66" s="131"/>
+      <c r="J66" s="131"/>
+      <c r="K66" s="131"/>
+      <c r="L66" s="131"/>
+      <c r="M66" s="131"/>
+      <c r="N66" s="131"/>
+      <c r="O66" s="131"/>
+      <c r="P66" s="131"/>
+      <c r="Q66" s="131"/>
+      <c r="R66" s="131"/>
+      <c r="S66" s="131"/>
+      <c r="T66" s="131"/>
+      <c r="U66" s="132"/>
+    </row>
+    <row r="67" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C67" s="20" t="s">
         <v>110</v>
       </c>
@@ -19170,11 +19167,11 @@
       </c>
       <c r="F67" s="36">
         <f>'Inputs Non-Residential'!D46*-1</f>
-        <v>-22500</v>
+        <v>0</v>
       </c>
       <c r="G67" s="36"/>
       <c r="H67" s="36" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I67" s="36"/>
       <c r="J67" s="36">
@@ -19183,7 +19180,7 @@
       </c>
       <c r="K67" s="36">
         <f>(F67*$J$2)/1000</f>
-        <v>-19.350000000000001</v>
+        <v>0</v>
       </c>
       <c r="L67" s="36"/>
       <c r="M67" s="36" t="str">
@@ -19197,7 +19194,7 @@
       </c>
       <c r="P67" s="36">
         <f>(F67*$J$2)/1000</f>
-        <v>-19.350000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q67" s="37"/>
       <c r="R67" s="37" t="str">
@@ -19211,10 +19208,10 @@
       </c>
       <c r="U67" s="44">
         <f>F67*$T$2</f>
-        <v>-6502.4999999999991</v>
-      </c>
-    </row>
-    <row r="68" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E68" s="14"/>
       <c r="F68" s="14"/>
       <c r="G68" s="14"/>
@@ -19228,30 +19225,30 @@
       <c r="O68" s="14"/>
       <c r="P68" s="14"/>
     </row>
-    <row r="69" spans="3:21" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="C69" s="132" t="s">
+    <row r="69" spans="3:21" ht="17.399999999999999" x14ac:dyDescent="0.35">
+      <c r="C69" s="130" t="s">
         <v>108</v>
       </c>
-      <c r="D69" s="133"/>
-      <c r="E69" s="133"/>
-      <c r="F69" s="133"/>
-      <c r="G69" s="133"/>
-      <c r="H69" s="133"/>
-      <c r="I69" s="133"/>
-      <c r="J69" s="133"/>
-      <c r="K69" s="133"/>
-      <c r="L69" s="133"/>
-      <c r="M69" s="133"/>
-      <c r="N69" s="133"/>
-      <c r="O69" s="133"/>
-      <c r="P69" s="133"/>
-      <c r="Q69" s="133"/>
-      <c r="R69" s="133"/>
-      <c r="S69" s="133"/>
-      <c r="T69" s="133"/>
-      <c r="U69" s="134"/>
-    </row>
-    <row r="70" spans="3:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="D69" s="131"/>
+      <c r="E69" s="131"/>
+      <c r="F69" s="131"/>
+      <c r="G69" s="131"/>
+      <c r="H69" s="131"/>
+      <c r="I69" s="131"/>
+      <c r="J69" s="131"/>
+      <c r="K69" s="131"/>
+      <c r="L69" s="131"/>
+      <c r="M69" s="131"/>
+      <c r="N69" s="131"/>
+      <c r="O69" s="131"/>
+      <c r="P69" s="131"/>
+      <c r="Q69" s="131"/>
+      <c r="R69" s="131"/>
+      <c r="S69" s="131"/>
+      <c r="T69" s="131"/>
+      <c r="U69" s="132"/>
+    </row>
+    <row r="70" spans="3:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C70" s="32" t="s">
         <v>109</v>
       </c>
@@ -19259,9 +19256,9 @@
       <c r="E70" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="F70" s="72" t="str">
+      <c r="F70" s="72">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
+        <v>0</v>
       </c>
       <c r="G70" s="8"/>
       <c r="H70" s="8" t="s">
@@ -19271,9 +19268,9 @@
       <c r="J70" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="K70" s="72" t="str">
+      <c r="K70" s="72">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
+        <v>0</v>
       </c>
       <c r="M70" s="72" t="s">
         <v>192</v>
@@ -19282,9 +19279,9 @@
       <c r="O70" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="P70" s="72" t="str">
+      <c r="P70" s="72">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
+        <v>0</v>
       </c>
       <c r="R70" s="8" t="s">
         <v>105</v>
@@ -19293,23 +19290,23 @@
       <c r="T70" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="U70" s="78" t="str">
+      <c r="U70" s="78">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
-      </c>
-    </row>
-    <row r="71" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C71" s="19" t="s">
         <v>1</v>
       </c>
       <c r="D71" s="14"/>
       <c r="E71" s="14">
         <f>E15</f>
-        <v>517345.39124999999</v>
+        <v>0</v>
       </c>
       <c r="F71" s="14">
         <f>F15</f>
-        <v>315070.15649999998</v>
+        <v>0</v>
       </c>
       <c r="G71" s="14"/>
       <c r="H71" t="s">
@@ -19318,11 +19315,11 @@
       <c r="I71" s="14"/>
       <c r="J71" s="14">
         <f>J15</f>
-        <v>444.91703647500003</v>
+        <v>0</v>
       </c>
       <c r="K71" s="14">
         <f>K15</f>
-        <v>270.96033459</v>
+        <v>0</v>
       </c>
       <c r="L71" s="14"/>
       <c r="M71" t="s">
@@ -19331,11 +19328,11 @@
       <c r="N71" s="14"/>
       <c r="O71" s="14">
         <f>O15</f>
-        <v>444.91703647500003</v>
+        <v>0</v>
       </c>
       <c r="P71" s="14">
         <f>P15</f>
-        <v>270.96033459</v>
+        <v>0</v>
       </c>
       <c r="Q71" s="14"/>
       <c r="R71" t="s">
@@ -19344,25 +19341,25 @@
       <c r="S71" s="14"/>
       <c r="T71" s="104">
         <f>T15</f>
-        <v>149512.81807124999</v>
+        <v>0</v>
       </c>
       <c r="U71" s="40">
         <f>U15</f>
-        <v>91055.275228499988</v>
-      </c>
-    </row>
-    <row r="72" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C72" s="19" t="s">
         <v>2</v>
       </c>
       <c r="D72" s="14"/>
       <c r="E72" s="14">
         <f>E25</f>
-        <v>14261.706693548385</v>
+        <v>0</v>
       </c>
       <c r="F72" s="14">
         <f>F25</f>
-        <v>14142.873676470586</v>
+        <v>0</v>
       </c>
       <c r="G72" s="14"/>
       <c r="H72" t="s">
@@ -19371,11 +19368,11 @@
       <c r="I72" s="14"/>
       <c r="J72" s="14">
         <f>J25</f>
-        <v>12.265067756451614</v>
+        <v>0</v>
       </c>
       <c r="K72" s="14">
         <f>K25</f>
-        <v>12.162871361764708</v>
+        <v>0</v>
       </c>
       <c r="L72" s="14"/>
       <c r="M72" t="s">
@@ -19384,11 +19381,11 @@
       <c r="N72" s="14"/>
       <c r="O72" s="14">
         <f>O25</f>
-        <v>12.265067756451614</v>
+        <v>0</v>
       </c>
       <c r="P72" s="14">
         <f>P25</f>
-        <v>12.162871361764708</v>
+        <v>0</v>
       </c>
       <c r="Q72" s="14"/>
       <c r="R72" t="s">
@@ -19397,25 +19394,25 @@
       <c r="S72" s="14"/>
       <c r="T72" s="104">
         <f>T25</f>
-        <v>14261.706693548385</v>
+        <v>0</v>
       </c>
       <c r="U72" s="40">
         <f>U25</f>
-        <v>14142.873676470586</v>
-      </c>
-    </row>
-    <row r="73" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C73" s="19" t="s">
         <v>230</v>
       </c>
       <c r="D73" s="14"/>
       <c r="E73" s="14">
         <f>E36</f>
-        <v>237578.41133081153</v>
+        <v>0</v>
       </c>
       <c r="F73" s="14">
         <f>F36</f>
-        <v>99649.712389857581</v>
+        <v>0</v>
       </c>
       <c r="G73" s="14"/>
       <c r="H73" t="s">
@@ -19424,11 +19421,11 @@
       <c r="I73" s="14"/>
       <c r="J73" s="14">
         <f>J36</f>
-        <v>56.773512744497907</v>
+        <v>0</v>
       </c>
       <c r="K73" s="14">
         <f>K36</f>
-        <v>30.896724855277501</v>
+        <v>0</v>
       </c>
       <c r="L73" s="14"/>
       <c r="M73" t="s">
@@ -19437,11 +19434,11 @@
       <c r="N73" s="14"/>
       <c r="O73" s="14">
         <f>O36</f>
-        <v>51.123312744497909</v>
+        <v>0</v>
       </c>
       <c r="P73" s="14">
         <f>P36</f>
-        <v>30.896724855277501</v>
+        <v>0</v>
       </c>
       <c r="Q73" s="14"/>
       <c r="R73" t="s">
@@ -19450,25 +19447,25 @@
       <c r="S73" s="14"/>
       <c r="T73" s="104">
         <f>T36</f>
-        <v>68660.160874604524</v>
+        <v>0</v>
       </c>
       <c r="U73" s="40">
         <f>U36</f>
-        <v>28798.766880668838</v>
-      </c>
-    </row>
-    <row r="74" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C74" s="19" t="s">
         <v>208</v>
       </c>
       <c r="D74" s="14"/>
       <c r="E74" s="14">
         <f>E46</f>
-        <v>19730.296933828653</v>
+        <v>0</v>
       </c>
       <c r="F74" s="14">
         <f>F46</f>
-        <v>19615.687057314361</v>
+        <v>0</v>
       </c>
       <c r="G74" s="14"/>
       <c r="H74" t="s">
@@ -19477,11 +19474,11 @@
       <c r="I74" s="14"/>
       <c r="J74" s="14">
         <f>J46</f>
-        <v>16.968055363092642</v>
+        <v>0</v>
       </c>
       <c r="K74" s="14">
         <f>K46</f>
-        <v>16.869490869290352</v>
+        <v>0</v>
       </c>
       <c r="L74" s="14"/>
       <c r="M74" t="s">
@@ -19490,11 +19487,11 @@
       <c r="N74" s="14"/>
       <c r="O74" s="14">
         <f>O46</f>
-        <v>16.968055363092642</v>
+        <v>0</v>
       </c>
       <c r="P74" s="14">
         <f>P46</f>
-        <v>16.869490869290352</v>
+        <v>0</v>
       </c>
       <c r="Q74" s="14"/>
       <c r="R74" t="s">
@@ -19503,25 +19500,25 @@
       <c r="S74" s="14"/>
       <c r="T74" s="104">
         <f>T46</f>
-        <v>5702.05581387648</v>
+        <v>0</v>
       </c>
       <c r="U74" s="40">
         <f>U46</f>
-        <v>5668.9335595638495</v>
-      </c>
-    </row>
-    <row r="75" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C75" s="19" t="s">
         <v>207</v>
       </c>
       <c r="D75" s="14"/>
       <c r="E75" s="14">
         <f>E57</f>
-        <v>4107.1840738384872</v>
+        <v>0</v>
       </c>
       <c r="F75" s="14">
         <f>F57</f>
-        <v>4026.586949676268</v>
+        <v>0</v>
       </c>
       <c r="G75" s="14"/>
       <c r="H75" t="s">
@@ -19530,11 +19527,11 @@
       <c r="I75" s="14"/>
       <c r="J75" s="14">
         <f>J57</f>
-        <v>3.532178303501099</v>
+        <v>0</v>
       </c>
       <c r="K75" s="14">
         <f>K57</f>
-        <v>3.4628647767215899</v>
+        <v>0</v>
       </c>
       <c r="L75" s="14"/>
       <c r="M75" t="s">
@@ -19543,11 +19540,11 @@
       <c r="N75" s="14"/>
       <c r="O75" s="14">
         <f>O57</f>
-        <v>3.532178303501099</v>
+        <v>0</v>
       </c>
       <c r="P75" s="14">
         <f>P57</f>
-        <v>3.4628647767215899</v>
+        <v>0</v>
       </c>
       <c r="Q75" s="14"/>
       <c r="R75" t="s">
@@ -19556,25 +19553,25 @@
       <c r="S75" s="14"/>
       <c r="T75" s="104">
         <f>T57</f>
-        <v>1186.9761973393227</v>
+        <v>0</v>
       </c>
       <c r="U75" s="40">
         <f>U57</f>
-        <v>1163.6836284564413</v>
-      </c>
-    </row>
-    <row r="76" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C76" s="19" t="s">
         <v>234</v>
       </c>
       <c r="D76" s="14"/>
       <c r="E76" s="14">
         <f>E64</f>
-        <v>7393.7999999999993</v>
+        <v>0</v>
       </c>
       <c r="F76" s="14">
         <f>F64</f>
-        <v>7393.7999999999993</v>
+        <v>0</v>
       </c>
       <c r="G76" s="14"/>
       <c r="H76" t="s">
@@ -19583,11 +19580,11 @@
       <c r="I76" s="14"/>
       <c r="J76" s="14">
         <f>J64</f>
-        <v>6.3586679999999998</v>
+        <v>0</v>
       </c>
       <c r="K76" s="14">
         <f>K64</f>
-        <v>6.3586679999999998</v>
+        <v>0</v>
       </c>
       <c r="L76" s="14"/>
       <c r="M76" t="s">
@@ -19596,11 +19593,11 @@
       <c r="N76" s="14"/>
       <c r="O76" s="14">
         <f>O64</f>
-        <v>6.3586679999999998</v>
+        <v>0</v>
       </c>
       <c r="P76" s="14">
         <f>P64</f>
-        <v>6.3586679999999998</v>
+        <v>0</v>
       </c>
       <c r="Q76" s="14"/>
       <c r="R76" t="s">
@@ -19609,14 +19606,14 @@
       <c r="S76" s="14"/>
       <c r="T76" s="104">
         <f>T64</f>
-        <v>2136.8081999999995</v>
+        <v>0</v>
       </c>
       <c r="U76" s="40">
         <f>U64</f>
-        <v>2136.8081999999995</v>
-      </c>
-    </row>
-    <row r="77" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C77" s="19" t="s">
         <v>100</v>
       </c>
@@ -19627,7 +19624,7 @@
       </c>
       <c r="F77" s="14">
         <f>F67</f>
-        <v>-22500</v>
+        <v>0</v>
       </c>
       <c r="G77" s="14"/>
       <c r="H77" t="s">
@@ -19640,7 +19637,7 @@
       </c>
       <c r="K77" s="14">
         <f>K67</f>
-        <v>-19.350000000000001</v>
+        <v>0</v>
       </c>
       <c r="L77" s="14"/>
       <c r="M77" t="s">
@@ -19653,7 +19650,7 @@
       </c>
       <c r="P77" s="14">
         <f>P67</f>
-        <v>-19.350000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q77" s="14"/>
       <c r="R77" t="s">
@@ -19666,21 +19663,21 @@
       </c>
       <c r="U77" s="40">
         <f>U67</f>
-        <v>-6502.4999999999991</v>
-      </c>
-    </row>
-    <row r="78" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C78" s="66" t="s">
         <v>94</v>
       </c>
       <c r="D78" s="17"/>
       <c r="E78" s="17">
         <f>SUM(E71:E77)</f>
-        <v>800416.7902820271</v>
+        <v>0</v>
       </c>
       <c r="F78" s="17">
         <f>SUM(F71:F77)</f>
-        <v>437398.81657331879</v>
+        <v>0</v>
       </c>
       <c r="G78" s="17"/>
       <c r="H78" s="17" t="str">
@@ -19690,15 +19687,15 @@
       <c r="I78" s="17"/>
       <c r="J78" s="17">
         <f>SUM(J71:J77)</f>
-        <v>540.81451864254336</v>
+        <v>0</v>
       </c>
       <c r="K78" s="17">
         <f>SUM(K71:K77)</f>
-        <v>321.36095445305415</v>
+        <v>0</v>
       </c>
       <c r="L78" s="17">
         <f>K78-J78</f>
-        <v>-219.45356418948921</v>
+        <v>0</v>
       </c>
       <c r="M78" s="17" t="str">
         <f>H78</f>
@@ -19707,11 +19704,11 @@
       <c r="N78" s="17"/>
       <c r="O78" s="17">
         <f>SUM(O71:O77)</f>
-        <v>535.16431864254332</v>
+        <v>0</v>
       </c>
       <c r="P78" s="17">
         <f>SUM(P71:P77)</f>
-        <v>321.36095445305415</v>
+        <v>0</v>
       </c>
       <c r="Q78" s="17"/>
       <c r="R78" s="1" t="s">
@@ -19720,14 +19717,14 @@
       <c r="S78" s="17"/>
       <c r="T78" s="110">
         <f>SUM(T71:T77)</f>
-        <v>241460.52585061869</v>
+        <v>0</v>
       </c>
       <c r="U78" s="111">
         <f>SUM(U71:U77)</f>
-        <v>136463.84117365969</v>
-      </c>
-    </row>
-    <row r="79" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C79" s="34"/>
       <c r="D79" s="65"/>
       <c r="E79" s="65"/>
@@ -19738,9 +19735,9 @@
       </c>
       <c r="I79" s="65"/>
       <c r="J79" s="65"/>
-      <c r="K79" s="65">
+      <c r="K79" s="65" t="e">
         <f>1-(K78/J78)</f>
-        <v>0.40578341857449129</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="L79" s="35"/>
       <c r="M79" s="35"/>
@@ -19754,11 +19751,11 @@
       <c r="S79" s="79"/>
       <c r="T79" s="115">
         <f>T78-U78</f>
-        <v>104996.684676959</v>
+        <v>0</v>
       </c>
       <c r="U79" s="43"/>
     </row>
-    <row r="80" spans="3:21" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="17"/>
@@ -19778,26 +19775,26 @@
       <c r="T80" s="17"/>
       <c r="U80" s="17"/>
     </row>
-    <row r="81" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="82" spans="3:21" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="C82" s="132" t="s">
+    <row r="81" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="82" spans="3:21" ht="17.399999999999999" x14ac:dyDescent="0.35">
+      <c r="C82" s="130" t="s">
         <v>186</v>
       </c>
-      <c r="D82" s="133"/>
-      <c r="E82" s="133"/>
-      <c r="F82" s="133"/>
-      <c r="G82" s="133"/>
-      <c r="H82" s="133"/>
-      <c r="I82" s="133"/>
-      <c r="J82" s="133"/>
-      <c r="K82" s="134"/>
+      <c r="D82" s="131"/>
+      <c r="E82" s="131"/>
+      <c r="F82" s="131"/>
+      <c r="G82" s="131"/>
+      <c r="H82" s="131"/>
+      <c r="I82" s="131"/>
+      <c r="J82" s="131"/>
+      <c r="K82" s="132"/>
       <c r="L82" s="92"/>
       <c r="M82" s="92"/>
       <c r="N82" s="92"/>
       <c r="O82" s="92"/>
       <c r="P82" s="92"/>
     </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C83" s="19" t="s">
         <v>181</v>
       </c>
@@ -19819,7 +19816,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="84" spans="3:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C84" s="63" t="s">
         <v>185</v>
       </c>
@@ -19846,7 +19843,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="85" spans="3:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:21" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C85" s="64" t="s">
         <v>182</v>
       </c>
@@ -19875,38 +19872,38 @@
       </c>
       <c r="O85" s="14"/>
     </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C86" s="67"/>
       <c r="D86" s="67"/>
       <c r="G86" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="87" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="88" spans="3:21" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="C88" s="132" t="s">
-        <v>241</v>
-      </c>
-      <c r="D88" s="133"/>
-      <c r="E88" s="133"/>
-      <c r="F88" s="133"/>
-      <c r="G88" s="133"/>
-      <c r="H88" s="133"/>
-      <c r="I88" s="133"/>
-      <c r="J88" s="133"/>
-      <c r="K88" s="133"/>
-      <c r="L88" s="133"/>
-      <c r="M88" s="133"/>
-      <c r="N88" s="133"/>
-      <c r="O88" s="133"/>
-      <c r="P88" s="133"/>
-      <c r="Q88" s="133"/>
-      <c r="R88" s="133"/>
-      <c r="S88" s="133"/>
-      <c r="T88" s="133"/>
-      <c r="U88" s="134"/>
-    </row>
-    <row r="89" spans="3:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="88" spans="3:21" ht="17.399999999999999" x14ac:dyDescent="0.35">
+      <c r="C88" s="130" t="s">
+        <v>240</v>
+      </c>
+      <c r="D88" s="131"/>
+      <c r="E88" s="131"/>
+      <c r="F88" s="131"/>
+      <c r="G88" s="131"/>
+      <c r="H88" s="131"/>
+      <c r="I88" s="131"/>
+      <c r="J88" s="131"/>
+      <c r="K88" s="131"/>
+      <c r="L88" s="131"/>
+      <c r="M88" s="131"/>
+      <c r="N88" s="131"/>
+      <c r="O88" s="131"/>
+      <c r="P88" s="131"/>
+      <c r="Q88" s="131"/>
+      <c r="R88" s="131"/>
+      <c r="S88" s="131"/>
+      <c r="T88" s="131"/>
+      <c r="U88" s="132"/>
+    </row>
+    <row r="89" spans="3:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C89" s="32" t="s">
         <v>109</v>
       </c>
@@ -19914,9 +19911,9 @@
       <c r="E89" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="F89" s="72" t="str">
+      <c r="F89" s="72">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
+        <v>0</v>
       </c>
       <c r="G89" s="8"/>
       <c r="H89" s="8" t="s">
@@ -19926,9 +19923,9 @@
       <c r="J89" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="K89" s="72" t="str">
+      <c r="K89" s="72">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
+        <v>0</v>
       </c>
       <c r="M89" s="72" t="s">
         <v>192</v>
@@ -19937,9 +19934,9 @@
       <c r="O89" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="P89" s="72" t="str">
+      <c r="P89" s="72">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
+        <v>0</v>
       </c>
       <c r="R89" s="8" t="s">
         <v>105</v>
@@ -19948,23 +19945,23 @@
       <c r="T89" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="U89" s="78" t="str">
+      <c r="U89" s="78">
         <f>'Inputs Non-Residential'!D5</f>
-        <v>123 Address</v>
-      </c>
-    </row>
-    <row r="90" spans="3:21" ht="30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C90" s="63" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D90" s="14"/>
       <c r="E90" s="14">
         <f t="shared" ref="E90:F95" si="17">E9+E19+E29+E40+E50</f>
-        <v>338427.68153202703</v>
+        <v>0</v>
       </c>
       <c r="F90" s="14">
         <f t="shared" si="17"/>
-        <v>307684.06257331884</v>
+        <v>0</v>
       </c>
       <c r="G90" s="14"/>
       <c r="H90" t="str">
@@ -19975,11 +19972,11 @@
       <c r="I90" s="14"/>
       <c r="J90" s="14">
         <f t="shared" ref="J90:K95" si="18">J9+J19+J29+J40+J50</f>
-        <v>291.0478061175433</v>
+        <v>0</v>
       </c>
       <c r="K90" s="14">
         <f t="shared" si="18"/>
-        <v>264.60829381305416</v>
+        <v>0</v>
       </c>
       <c r="L90" s="14"/>
       <c r="M90" t="str">
@@ -19990,11 +19987,11 @@
       <c r="N90" s="14"/>
       <c r="O90" s="14">
         <f t="shared" ref="O90:P95" si="19">O9+O19+O29+O40+O50</f>
-        <v>291.0478061175433</v>
+        <v>0</v>
       </c>
       <c r="P90" s="14">
         <f t="shared" si="19"/>
-        <v>264.60829381305416</v>
+        <v>0</v>
       </c>
       <c r="Q90" s="14"/>
       <c r="R90" t="str">
@@ -20005,25 +20002,25 @@
       <c r="S90" s="14"/>
       <c r="T90" s="33">
         <f t="shared" ref="T90:U95" si="20">T9+T19+T29+T40+T50</f>
-        <v>97805.599962755819</v>
+        <v>0</v>
       </c>
       <c r="U90" s="40">
         <f t="shared" si="20"/>
-        <v>88920.69408368913</v>
-      </c>
-    </row>
-    <row r="91" spans="3:21" ht="30" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="3:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C91" s="63" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D91" s="14"/>
       <c r="E91" s="14">
         <f t="shared" si="17"/>
-        <v>218748.6</v>
+        <v>0</v>
       </c>
       <c r="F91" s="14">
         <f t="shared" si="17"/>
-        <v>81249.48000000001</v>
+        <v>0</v>
       </c>
       <c r="G91" s="14"/>
       <c r="H91" t="str">
@@ -20034,11 +20031,11 @@
       <c r="I91" s="14"/>
       <c r="J91" s="14">
         <f t="shared" si="18"/>
-        <v>40.579875000000001</v>
+        <v>0</v>
       </c>
       <c r="K91" s="14">
         <f t="shared" si="18"/>
-        <v>15.072524999999999</v>
+        <v>0</v>
       </c>
       <c r="L91" s="14"/>
       <c r="M91" t="str">
@@ -20049,11 +20046,11 @@
       <c r="N91" s="14"/>
       <c r="O91" s="14">
         <f t="shared" si="19"/>
-        <v>40.579875000000001</v>
+        <v>0</v>
       </c>
       <c r="P91" s="14">
         <f t="shared" si="19"/>
-        <v>15.072524999999999</v>
+        <v>0</v>
       </c>
       <c r="Q91" s="14"/>
       <c r="R91" t="str">
@@ -20064,14 +20061,14 @@
       <c r="S91" s="14"/>
       <c r="T91" s="33">
         <f t="shared" si="20"/>
-        <v>27562.500000000004</v>
+        <v>0</v>
       </c>
       <c r="U91" s="40">
         <f t="shared" si="20"/>
-        <v>10237.500000000002</v>
-      </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C92" s="19" t="s">
         <v>145</v>
       </c>
@@ -20127,18 +20124,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C93" s="19" t="s">
         <v>98</v>
       </c>
       <c r="D93" s="14"/>
       <c r="E93" s="14">
         <f t="shared" si="17"/>
-        <v>193701.2</v>
+        <v>0</v>
       </c>
       <c r="F93" s="14">
         <f t="shared" si="17"/>
-        <v>34833.199999999997</v>
+        <v>0</v>
       </c>
       <c r="G93" s="14"/>
       <c r="H93" t="str">
@@ -20148,11 +20145,11 @@
       <c r="I93" s="14"/>
       <c r="J93" s="14">
         <f t="shared" si="18"/>
-        <v>166.583032</v>
+        <v>0</v>
       </c>
       <c r="K93" s="14">
         <f t="shared" si="18"/>
-        <v>29.956552000000002</v>
+        <v>0</v>
       </c>
       <c r="L93" s="14"/>
       <c r="M93" t="str">
@@ -20162,11 +20159,11 @@
       <c r="N93" s="14"/>
       <c r="O93" s="14">
         <f t="shared" si="19"/>
-        <v>160.93283199999999</v>
+        <v>0</v>
       </c>
       <c r="P93" s="14">
         <f t="shared" si="19"/>
-        <v>29.956552000000002</v>
+        <v>0</v>
       </c>
       <c r="Q93" s="14"/>
       <c r="R93" t="str">
@@ -20176,25 +20173,25 @@
       <c r="S93" s="14"/>
       <c r="T93" s="33">
         <f t="shared" si="20"/>
-        <v>55979.646800000002</v>
+        <v>0</v>
       </c>
       <c r="U93" s="40">
         <f t="shared" si="20"/>
-        <v>10066.794799999998</v>
-      </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C94" s="19" t="s">
         <v>99</v>
       </c>
       <c r="D94" s="14"/>
       <c r="E94" s="14">
         <f t="shared" si="17"/>
-        <v>34406.641250000001</v>
+        <v>0</v>
       </c>
       <c r="F94" s="14">
         <f t="shared" si="17"/>
-        <v>20999.406499999997</v>
+        <v>0</v>
       </c>
       <c r="G94" s="14"/>
       <c r="H94" t="str">
@@ -20204,11 +20201,11 @@
       <c r="I94" s="14"/>
       <c r="J94" s="14">
         <f t="shared" si="18"/>
-        <v>29.589711474999998</v>
+        <v>0</v>
       </c>
       <c r="K94" s="14">
         <f t="shared" si="18"/>
-        <v>18.059489589999998</v>
+        <v>0</v>
       </c>
       <c r="L94" s="14"/>
       <c r="M94" t="str">
@@ -20218,11 +20215,11 @@
       <c r="N94" s="14"/>
       <c r="O94" s="14">
         <f t="shared" si="19"/>
-        <v>29.589711474999998</v>
+        <v>0</v>
       </c>
       <c r="P94" s="14">
         <f t="shared" si="19"/>
-        <v>18.059489589999998</v>
+        <v>0</v>
       </c>
       <c r="Q94" s="14"/>
       <c r="R94" t="str">
@@ -20232,25 +20229,25 @@
       <c r="S94" s="14"/>
       <c r="T94" s="33">
         <f t="shared" si="20"/>
-        <v>9943.519321249998</v>
+        <v>0</v>
       </c>
       <c r="U94" s="40">
         <f t="shared" si="20"/>
-        <v>6068.8284784999996</v>
-      </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C95" s="19" t="s">
         <v>28</v>
       </c>
       <c r="D95" s="14"/>
       <c r="E95" s="14">
         <f t="shared" si="17"/>
-        <v>7738.8674999999985</v>
+        <v>0</v>
       </c>
       <c r="F95" s="14">
         <f t="shared" si="17"/>
-        <v>7738.8674999999985</v>
+        <v>0</v>
       </c>
       <c r="G95" s="14"/>
       <c r="H95" t="str">
@@ -20260,11 +20257,11 @@
       <c r="I95" s="14"/>
       <c r="J95" s="14">
         <f t="shared" si="18"/>
-        <v>6.6554260499999991</v>
+        <v>0</v>
       </c>
       <c r="K95" s="14">
         <f t="shared" si="18"/>
-        <v>6.6554260499999991</v>
+        <v>0</v>
       </c>
       <c r="L95" s="14"/>
       <c r="M95" t="str">
@@ -20274,11 +20271,11 @@
       <c r="N95" s="14"/>
       <c r="O95" s="14">
         <f t="shared" si="19"/>
-        <v>6.6554260499999991</v>
+        <v>0</v>
       </c>
       <c r="P95" s="14">
         <f t="shared" si="19"/>
-        <v>6.6554260499999991</v>
+        <v>0</v>
       </c>
       <c r="Q95" s="14"/>
       <c r="R95" t="str">
@@ -20288,25 +20285,25 @@
       <c r="S95" s="14"/>
       <c r="T95" s="33">
         <f t="shared" si="20"/>
-        <v>2236.5327074999996</v>
+        <v>0</v>
       </c>
       <c r="U95" s="40">
         <f t="shared" si="20"/>
-        <v>2236.5327074999996</v>
-      </c>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C96" s="19" t="s">
         <v>234</v>
       </c>
       <c r="D96" s="14"/>
       <c r="E96" s="14">
         <f>E76</f>
-        <v>7393.7999999999993</v>
+        <v>0</v>
       </c>
       <c r="F96" s="14">
         <f>F76</f>
-        <v>7393.7999999999993</v>
+        <v>0</v>
       </c>
       <c r="G96" s="14"/>
       <c r="H96" t="str">
@@ -20316,11 +20313,11 @@
       <c r="I96" s="14"/>
       <c r="J96" s="14">
         <f>J76</f>
-        <v>6.3586679999999998</v>
+        <v>0</v>
       </c>
       <c r="K96" s="14">
         <f>K76</f>
-        <v>6.3586679999999998</v>
+        <v>0</v>
       </c>
       <c r="L96" s="14"/>
       <c r="M96" t="str">
@@ -20330,11 +20327,11 @@
       <c r="N96" s="14"/>
       <c r="O96" s="14">
         <f>O76</f>
-        <v>6.3586679999999998</v>
+        <v>0</v>
       </c>
       <c r="P96" s="14">
         <f>P76</f>
-        <v>6.3586679999999998</v>
+        <v>0</v>
       </c>
       <c r="Q96" s="14"/>
       <c r="R96" t="str">
@@ -20344,25 +20341,25 @@
       <c r="S96" s="14"/>
       <c r="T96" s="33">
         <f>T76</f>
-        <v>2136.8081999999995</v>
+        <v>0</v>
       </c>
       <c r="U96" s="40">
         <f>U76</f>
-        <v>2136.8081999999995</v>
-      </c>
-    </row>
-    <row r="97" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C97" s="34" t="s">
         <v>94</v>
       </c>
       <c r="D97" s="36"/>
       <c r="E97" s="36">
         <f>SUM(E90:E96)</f>
-        <v>800416.7902820271</v>
+        <v>0</v>
       </c>
       <c r="F97" s="36">
         <f>SUM(F90:F95)</f>
-        <v>452505.0165733188</v>
+        <v>0</v>
       </c>
       <c r="G97" s="36"/>
       <c r="H97" s="38" t="str">
@@ -20372,11 +20369,11 @@
       <c r="I97" s="36"/>
       <c r="J97" s="35">
         <f>SUM(J90:J96)</f>
-        <v>540.81451864254325</v>
+        <v>0</v>
       </c>
       <c r="K97" s="35">
         <f>SUM(K90:K95)</f>
-        <v>334.35228645305415</v>
+        <v>0</v>
       </c>
       <c r="L97" s="36"/>
       <c r="M97" s="38" t="str">
@@ -20386,11 +20383,11 @@
       <c r="N97" s="35"/>
       <c r="O97" s="35">
         <f>O15+O25+O35+O46+O56</f>
-        <v>474.15015959454428</v>
+        <v>0</v>
       </c>
       <c r="P97" s="35">
         <f>P15+P25+P35+P46+P56</f>
-        <v>299.99269682105506</v>
+        <v>0</v>
       </c>
       <c r="Q97" s="36"/>
       <c r="R97" s="38" t="str">
@@ -20400,22 +20397,22 @@
       <c r="S97" s="36"/>
       <c r="T97" s="112">
         <f>T15+T25+T35+T46+T56</f>
-        <v>169476.58057867485</v>
+        <v>0</v>
       </c>
       <c r="U97" s="44">
         <f>U15+U25+U35+U46+U56</f>
-        <v>110867.08246453443</v>
-      </c>
-    </row>
-    <row r="98" spans="3:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C98" s="106" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D98" s="107"/>
       <c r="E98" s="107"/>
       <c r="F98" s="109">
         <f>E97-F97</f>
-        <v>347911.77370870829</v>
+        <v>0</v>
       </c>
       <c r="G98" s="108"/>
       <c r="H98" s="108" t="s">
@@ -20423,9 +20420,9 @@
       </c>
       <c r="I98" s="107"/>
       <c r="J98" s="107"/>
-      <c r="K98" s="107">
+      <c r="K98" s="107" t="e">
         <f>1-(K97/J97)</f>
-        <v>0.38176163004594255</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="L98" s="108"/>
       <c r="M98" s="108"/>
@@ -20440,11 +20437,16 @@
       <c r="T98" s="113"/>
       <c r="U98" s="114">
         <f>T97-U97</f>
-        <v>58609.498114140428</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="R3:S3"/>
     <mergeCell ref="C88:U88"/>
     <mergeCell ref="C7:U7"/>
     <mergeCell ref="C17:U17"/>
@@ -20455,11 +20457,6 @@
     <mergeCell ref="C27:U27"/>
     <mergeCell ref="C38:U38"/>
     <mergeCell ref="C48:U48"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="R3:S3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -20469,26 +20466,26 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC07E4BE-C962-4C7E-AA01-A850DDE55B29}">
   <dimension ref="B2:O24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="19.7109375" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.7109375" customWidth="1"/>
-    <col min="11" max="12" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.28515625" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="19.6640625" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" customWidth="1"/>
+    <col min="11" max="12" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.33203125" customWidth="1"/>
+    <col min="14" max="14" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="J2" s="131" t="s">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="J2" s="134" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="131"/>
-      <c r="L2" s="131"/>
-    </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="K2" s="134"/>
+      <c r="L2" s="134"/>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.3">
       <c r="J3">
         <v>3</v>
       </c>
@@ -20502,7 +20499,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>17</v>
       </c>
@@ -20525,7 +20522,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>18</v>
       </c>
@@ -20548,7 +20545,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>19</v>
       </c>
@@ -20571,7 +20568,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>22</v>
       </c>
@@ -20594,7 +20591,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>23</v>
       </c>
@@ -20602,7 +20599,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="I9" t="s">
         <v>42</v>
       </c>
@@ -20625,7 +20622,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
       <c r="I10">
         <v>6</v>
       </c>
@@ -20652,7 +20649,7 @@
         <v>33.538978056701609</v>
       </c>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>24</v>
       </c>
@@ -20670,7 +20667,7 @@
       <c r="N11" s="15"/>
       <c r="O11" s="15"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>25</v>
       </c>
@@ -20678,7 +20675,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>26</v>
       </c>
@@ -20686,7 +20683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>27</v>
       </c>
@@ -20697,12 +20694,12 @@
         <v>177</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
       <c r="I15" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>28</v>
       </c>
@@ -20719,7 +20716,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>29</v>
       </c>
@@ -20733,7 +20730,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>30</v>
       </c>
@@ -20748,7 +20745,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>31</v>
       </c>
@@ -20763,7 +20760,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>193</v>
       </c>
@@ -20777,7 +20774,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>102</v>
       </c>
@@ -20785,7 +20782,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="2" t="s">
         <v>18</v>
       </c>
@@ -20793,7 +20790,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="2" t="s">
         <v>19</v>
       </c>
@@ -20821,22 +20818,22 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BC94C4A-4031-4B7A-B54E-5F499B381D6C}">
   <dimension ref="B3:Q40"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
@@ -20880,7 +20877,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>112</v>
       </c>
@@ -20930,7 +20927,7 @@
         <v>30.298115896211506</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>119</v>
       </c>
@@ -20980,7 +20977,7 @@
         <v>5.7022058823529411</v>
       </c>
     </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>132</v>
       </c>
@@ -21030,7 +21027,7 @@
         <v>12.261522346368714</v>
       </c>
     </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>204</v>
       </c>
@@ -21080,7 +21077,7 @@
         <v>11.306772908366533</v>
       </c>
     </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>205</v>
       </c>
@@ -21130,7 +21127,7 @@
         <v>11.441176470588236</v>
       </c>
     </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>206</v>
       </c>
@@ -21180,7 +21177,7 @@
         <v>8.3451327433628322</v>
       </c>
     </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:17" x14ac:dyDescent="0.3">
       <c r="F10" s="15" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -21218,7 +21215,7 @@
         <v>8.6241457858769923</v>
       </c>
     </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:17" x14ac:dyDescent="0.3">
       <c r="F11" s="15" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -21259,7 +21256,7 @@
         <v>6.3094839142091157</v>
       </c>
     </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:17" x14ac:dyDescent="0.3">
       <c r="G12" t="s">
         <v>218</v>
       </c>
@@ -21295,10 +21292,10 @@
         <v>9.2532810635759333</v>
       </c>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:17" x14ac:dyDescent="0.3">
       <c r="Q13" s="15"/>
     </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>2</v>
       </c>
@@ -21321,7 +21318,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>120</v>
       </c>
@@ -21354,7 +21351,7 @@
         <v>11.504648556768091</v>
       </c>
     </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>121</v>
       </c>
@@ -21380,7 +21377,7 @@
         <v>52.291581108829568</v>
       </c>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>122</v>
       </c>
@@ -21427,7 +21424,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>123</v>
       </c>
@@ -21477,7 +21474,7 @@
         <v>36.023529411764706</v>
       </c>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>124</v>
       </c>
@@ -21527,7 +21524,7 @@
         <v>32.159430835152399</v>
       </c>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>125</v>
       </c>
@@ -21577,7 +21574,7 @@
         <v>44.576761240682856</v>
       </c>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>126</v>
       </c>
@@ -21627,7 +21624,7 @@
         <v>21.396190739206482</v>
       </c>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>127</v>
       </c>
@@ -21653,7 +21650,7 @@
         <v>9.4357682619647356</v>
       </c>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>128</v>
       </c>
@@ -21686,7 +21683,7 @@
         <v>33.538978056701609</v>
       </c>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>129</v>
       </c>
@@ -21712,7 +21709,7 @@
         <v>8.6748329621380851</v>
       </c>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>130</v>
       </c>
@@ -21738,7 +21735,7 @@
         <v>14.919491083533215</v>
       </c>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>131</v>
       </c>
@@ -21764,7 +21761,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.3">
       <c r="G28" t="s">
         <v>218</v>
       </c>
@@ -21773,7 +21770,7 @@
         <v>16.707620165569967</v>
       </c>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>207</v>
       </c>
@@ -21796,7 +21793,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>224</v>
       </c>
@@ -21822,7 +21819,7 @@
         <v>22.614721243775051</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>225</v>
       </c>
@@ -21848,7 +21845,7 @@
         <v>26.217015423911974</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>226</v>
       </c>
@@ -21874,7 +21871,7 @@
         <v>30.92134576040009</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>227</v>
       </c>
@@ -21900,7 +21897,7 @@
         <v>136.85220820189275</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>228</v>
       </c>
@@ -21926,7 +21923,7 @@
         <v>29.419473361910597</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>229</v>
       </c>
@@ -21952,7 +21949,7 @@
         <v>32.409725654967872</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
       <c r="F38" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
@@ -21966,7 +21963,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
       <c r="G40" t="s">
         <v>218</v>
       </c>
@@ -21983,48 +21980,48 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA06D635-BD0B-4E92-BB77-38BEC90462EF}">
   <dimension ref="A1:V73"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" style="24" customWidth="1"/>
-    <col min="2" max="2" width="4.7109375" style="21" customWidth="1"/>
-    <col min="3" max="3" width="35.7109375" style="21" customWidth="1"/>
-    <col min="4" max="4" width="19.28515625" style="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" style="21" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" style="21" customWidth="1"/>
+    <col min="1" max="1" width="8.44140625" style="24" customWidth="1"/>
+    <col min="2" max="2" width="4.6640625" style="21" customWidth="1"/>
+    <col min="3" max="3" width="35.6640625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5546875" style="21" customWidth="1"/>
     <col min="7" max="7" width="5" style="21" customWidth="1"/>
-    <col min="8" max="8" width="35.7109375" style="21" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" style="21" customWidth="1"/>
+    <col min="8" max="8" width="35.6640625" style="21" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" style="21" customWidth="1"/>
     <col min="10" max="10" width="16" style="21" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.7109375" style="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.6640625" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.6640625" style="21" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" style="21" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" style="21" customWidth="1"/>
-    <col min="15" max="15" width="10.7109375" style="21" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="35.7109375" style="21" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.85546875" style="24" customWidth="1"/>
-    <col min="18" max="19" width="8.85546875" style="24"/>
-    <col min="20" max="20" width="35.7109375" style="24" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.7109375" style="24" customWidth="1"/>
-    <col min="22" max="22" width="11.140625" style="24" customWidth="1"/>
-    <col min="23" max="16384" width="8.85546875" style="21"/>
+    <col min="14" max="14" width="12.5546875" style="21" customWidth="1"/>
+    <col min="15" max="15" width="10.6640625" style="21" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="35.6640625" style="21" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.88671875" style="24" customWidth="1"/>
+    <col min="18" max="19" width="8.88671875" style="24"/>
+    <col min="20" max="20" width="35.6640625" style="24" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.6640625" style="24" customWidth="1"/>
+    <col min="22" max="22" width="11.109375" style="24" customWidth="1"/>
+    <col min="23" max="16384" width="8.88671875" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" s="24" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:16" s="24" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:16" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B3" s="123" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="124"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="125"/>
+    <row r="1" spans="2:16" s="24" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:16" s="24" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="2:16" ht="17.399999999999999" x14ac:dyDescent="0.35">
+      <c r="B3" s="127" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="128"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="129"/>
       <c r="F3" s="24"/>
-      <c r="G3" s="127" t="s">
+      <c r="G3" s="124" t="s">
         <v>35</v>
       </c>
-      <c r="H3" s="128"/>
-      <c r="I3" s="128"/>
-      <c r="J3" s="129"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="126"/>
       <c r="K3" s="24"/>
       <c r="L3" s="24"/>
       <c r="M3" s="24"/>
@@ -22032,7 +22029,7 @@
       <c r="O3" s="24"/>
       <c r="P3" s="24"/>
     </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B4" s="23"/>
       <c r="C4" s="24"/>
       <c r="D4" s="24"/>
@@ -22049,14 +22046,12 @@
       <c r="O4" s="24"/>
       <c r="P4" s="24"/>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B5" s="23"/>
       <c r="C5" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="D5" s="55" t="s">
-        <v>237</v>
-      </c>
+      <c r="D5" s="55"/>
       <c r="E5" s="25"/>
       <c r="F5" s="24"/>
       <c r="G5" s="23"/>
@@ -22074,14 +22069,12 @@
       <c r="O5" s="24"/>
       <c r="P5" s="24"/>
     </row>
-    <row r="6" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B6" s="23"/>
       <c r="C6" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="53">
-        <v>150</v>
-      </c>
+      <c r="D6" s="53"/>
       <c r="E6" s="25" t="s">
         <v>5</v>
       </c>
@@ -22097,14 +22090,12 @@
       <c r="O6" s="24"/>
       <c r="P6" s="24"/>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B7" s="23"/>
       <c r="C7" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="53">
-        <v>250</v>
-      </c>
+      <c r="D7" s="53"/>
       <c r="E7" s="25" t="s">
         <v>5</v>
       </c>
@@ -22120,14 +22111,12 @@
       <c r="O7" s="24"/>
       <c r="P7" s="24"/>
     </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B8" s="23"/>
       <c r="C8" s="30" t="s">
         <v>230</v>
       </c>
-      <c r="D8" s="53">
-        <v>450</v>
-      </c>
+      <c r="D8" s="53"/>
       <c r="E8" s="25" t="s">
         <v>5</v>
       </c>
@@ -22145,14 +22134,12 @@
       <c r="O8" s="24"/>
       <c r="P8" s="24"/>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" s="23"/>
       <c r="C9" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="D9" s="53">
-        <v>350</v>
-      </c>
+      <c r="D9" s="53"/>
       <c r="E9" s="25" t="s">
         <v>5</v>
       </c>
@@ -22168,14 +22155,12 @@
       <c r="O9" s="24"/>
       <c r="P9" s="24"/>
     </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B10" s="23"/>
       <c r="C10" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="D10" s="53">
-        <v>100</v>
-      </c>
+      <c r="D10" s="53"/>
       <c r="E10" s="25" t="s">
         <v>5</v>
       </c>
@@ -22193,14 +22178,12 @@
       <c r="O10" s="24"/>
       <c r="P10" s="24"/>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B11" s="23"/>
       <c r="C11" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="53">
-        <v>300</v>
-      </c>
+      <c r="D11" s="53"/>
       <c r="E11" s="25" t="s">
         <v>5</v>
       </c>
@@ -22216,14 +22199,12 @@
       <c r="O11" s="24"/>
       <c r="P11" s="24"/>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B12" s="23"/>
       <c r="C12" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="53">
-        <v>250</v>
-      </c>
+      <c r="D12" s="53"/>
       <c r="E12" s="25" t="s">
         <v>5</v>
       </c>
@@ -22239,7 +22220,7 @@
       <c r="O12" s="24"/>
       <c r="P12" s="24"/>
     </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B13" s="23"/>
       <c r="C13" s="30" t="s">
         <v>133</v>
@@ -22258,7 +22239,7 @@
       <c r="O13" s="24"/>
       <c r="P13" s="24"/>
     </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B14" s="23"/>
       <c r="C14" s="30" t="s">
         <v>134</v>
@@ -22279,7 +22260,7 @@
       <c r="O14" s="24"/>
       <c r="P14" s="24"/>
     </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B15" s="23"/>
       <c r="C15" s="24"/>
       <c r="D15" s="24"/>
@@ -22296,7 +22277,7 @@
       <c r="O15" s="24"/>
       <c r="P15" s="24"/>
     </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B16" s="23"/>
       <c r="C16" s="30" t="s">
         <v>177</v>
@@ -22315,7 +22296,7 @@
       <c r="O16" s="24"/>
       <c r="P16" s="24"/>
     </row>
-    <row r="17" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="26"/>
       <c r="C17" s="22"/>
       <c r="D17" s="22"/>
@@ -22332,7 +22313,7 @@
       <c r="O17" s="24"/>
       <c r="P17" s="24"/>
     </row>
-    <row r="18" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B18" s="85"/>
       <c r="C18" s="24"/>
       <c r="D18" s="24"/>
@@ -22349,33 +22330,33 @@
       <c r="O18" s="24"/>
       <c r="P18" s="24"/>
     </row>
-    <row r="19" spans="2:22" s="24" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="2:22" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B20" s="123" t="s">
+    <row r="19" spans="2:22" s="24" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="2:22" ht="17.399999999999999" x14ac:dyDescent="0.35">
+      <c r="B20" s="127" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="124"/>
-      <c r="D20" s="124"/>
-      <c r="E20" s="124"/>
-      <c r="F20" s="124"/>
-      <c r="G20" s="124"/>
-      <c r="H20" s="124"/>
-      <c r="I20" s="124"/>
-      <c r="J20" s="124"/>
-      <c r="K20" s="124"/>
-      <c r="L20" s="124"/>
-      <c r="M20" s="124"/>
-      <c r="N20" s="124"/>
-      <c r="O20" s="124"/>
-      <c r="P20" s="124"/>
-      <c r="Q20" s="124"/>
-      <c r="R20" s="124"/>
-      <c r="S20" s="124"/>
-      <c r="T20" s="124"/>
-      <c r="U20" s="124"/>
-      <c r="V20" s="125"/>
-    </row>
-    <row r="21" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C20" s="128"/>
+      <c r="D20" s="128"/>
+      <c r="E20" s="128"/>
+      <c r="F20" s="128"/>
+      <c r="G20" s="128"/>
+      <c r="H20" s="128"/>
+      <c r="I20" s="128"/>
+      <c r="J20" s="128"/>
+      <c r="K20" s="128"/>
+      <c r="L20" s="128"/>
+      <c r="M20" s="128"/>
+      <c r="N20" s="128"/>
+      <c r="O20" s="128"/>
+      <c r="P20" s="128"/>
+      <c r="Q20" s="128"/>
+      <c r="R20" s="128"/>
+      <c r="S20" s="128"/>
+      <c r="T20" s="128"/>
+      <c r="U20" s="128"/>
+      <c r="V20" s="129"/>
+    </row>
+    <row r="21" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B21" s="23"/>
       <c r="C21" s="28"/>
       <c r="D21" s="24"/>
@@ -22393,7 +22374,7 @@
       <c r="P21" s="24"/>
       <c r="V21" s="25"/>
     </row>
-    <row r="22" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B22" s="90"/>
       <c r="C22" s="82" t="s">
         <v>1</v>
@@ -22422,9 +22403,9 @@
         <v>207</v>
       </c>
       <c r="U22" s="122"/>
-      <c r="V22" s="126"/>
-    </row>
-    <row r="23" spans="2:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="V22" s="123"/>
+    </row>
+    <row r="23" spans="2:22" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B23" s="90"/>
       <c r="C23" s="29" t="s">
         <v>11</v>
@@ -22470,7 +22451,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B24" s="90"/>
       <c r="C24" s="30" t="s">
         <v>6</v>
@@ -22512,7 +22493,7 @@
       </c>
       <c r="V24" s="89"/>
     </row>
-    <row r="25" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B25" s="90"/>
       <c r="C25" s="30" t="s">
         <v>7</v>
@@ -22569,7 +22550,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B26" s="90"/>
       <c r="C26" s="30" t="s">
         <v>13</v>
@@ -22621,7 +22602,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B27" s="90"/>
       <c r="C27" s="30" t="s">
         <v>28</v>
@@ -22659,7 +22640,7 @@
       </c>
       <c r="V27" s="88"/>
     </row>
-    <row r="28" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B28" s="90"/>
       <c r="C28" s="24"/>
       <c r="D28"/>
@@ -22679,7 +22660,7 @@
       <c r="P28" s="24"/>
       <c r="V28" s="25"/>
     </row>
-    <row r="29" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B29" s="90"/>
       <c r="C29" s="24" t="s">
         <v>143</v>
@@ -22699,7 +22680,7 @@
       <c r="P29" s="24"/>
       <c r="V29" s="25"/>
     </row>
-    <row r="30" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B30" s="90"/>
       <c r="C30" s="24"/>
       <c r="D30" s="24"/>
@@ -22717,7 +22698,7 @@
       <c r="P30" s="24"/>
       <c r="V30" s="25"/>
     </row>
-    <row r="31" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B31" s="90"/>
       <c r="C31" s="82" t="s">
         <v>144</v>
@@ -22747,16 +22728,14 @@
         <v>144</v>
       </c>
       <c r="U31" s="122"/>
-      <c r="V31" s="126"/>
-    </row>
-    <row r="32" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="V31" s="123"/>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B32" s="90"/>
       <c r="C32" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="D32" s="53">
-        <v>1100</v>
-      </c>
+      <c r="D32" s="53"/>
       <c r="E32" s="31" t="s">
         <v>103</v>
       </c>
@@ -22793,14 +22772,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B33" s="90"/>
       <c r="C33" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="D33" s="53">
-        <v>1100</v>
-      </c>
+      <c r="D33" s="53"/>
       <c r="E33" s="30" t="s">
         <v>103</v>
       </c>
@@ -22837,7 +22814,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B34" s="90"/>
       <c r="C34" s="31" t="s">
         <v>163</v>
@@ -22881,7 +22858,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B35" s="90"/>
       <c r="C35" s="30" t="s">
         <v>164</v>
@@ -22925,7 +22902,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B36" s="90"/>
       <c r="C36" s="30" t="s">
         <v>146</v>
@@ -22967,14 +22944,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B37" s="23"/>
       <c r="C37" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="D37" s="53">
-        <v>1100</v>
-      </c>
+      <c r="D37" s="53"/>
       <c r="E37" s="30" t="s">
         <v>103</v>
       </c>
@@ -23011,7 +22986,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B38" s="23"/>
       <c r="C38" s="24"/>
       <c r="E38" s="31"/>
@@ -23029,14 +23004,12 @@
       <c r="U38" s="21"/>
       <c r="V38" s="89"/>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B39" s="23"/>
       <c r="C39" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="D39" s="54">
-        <v>1000</v>
-      </c>
+      <c r="D39" s="54"/>
       <c r="E39" s="30" t="s">
         <v>103</v>
       </c>
@@ -23073,14 +23046,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B40" s="23"/>
       <c r="C40" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="D40" s="54">
-        <v>1000</v>
-      </c>
+      <c r="D40" s="54"/>
       <c r="E40" s="31" t="s">
         <v>103</v>
       </c>
@@ -23117,7 +23088,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B41" s="23"/>
       <c r="C41" s="31" t="s">
         <v>165</v>
@@ -23161,7 +23132,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B42" s="23"/>
       <c r="C42" s="30" t="s">
         <v>166</v>
@@ -23205,7 +23176,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B43" s="23"/>
       <c r="C43" s="30" t="s">
         <v>148</v>
@@ -23247,7 +23218,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B44" s="23"/>
       <c r="C44" s="30" t="s">
         <v>149</v>
@@ -23289,7 +23260,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B45" s="23"/>
       <c r="C45" s="24"/>
       <c r="D45" s="24"/>
@@ -23307,14 +23278,12 @@
       <c r="P45" s="47"/>
       <c r="V45" s="25"/>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B46" s="23"/>
       <c r="C46" s="45" t="s">
         <v>155</v>
       </c>
-      <c r="D46" s="84">
-        <v>22500</v>
-      </c>
+      <c r="D46" s="84"/>
       <c r="E46" s="24" t="s">
         <v>15</v>
       </c>
@@ -23331,7 +23300,7 @@
       <c r="P46" s="24"/>
       <c r="V46" s="25"/>
     </row>
-    <row r="47" spans="2:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="26"/>
       <c r="C47" s="86"/>
       <c r="D47" s="86"/>
@@ -23354,7 +23323,7 @@
       <c r="U47" s="22"/>
       <c r="V47" s="27"/>
     </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B48" s="24"/>
       <c r="C48"/>
       <c r="D48"/>
@@ -23371,7 +23340,7 @@
       <c r="O48" s="24"/>
       <c r="P48" s="24"/>
     </row>
-    <row r="49" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B49" s="24"/>
       <c r="C49" s="24"/>
       <c r="D49" s="24"/>
@@ -23388,32 +23357,32 @@
       <c r="O49" s="24"/>
       <c r="P49" s="24"/>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B50" s="127" t="s">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B50" s="124" t="s">
         <v>16</v>
       </c>
-      <c r="C50" s="128"/>
-      <c r="D50" s="128"/>
-      <c r="E50" s="128"/>
-      <c r="F50" s="128"/>
-      <c r="G50" s="128"/>
-      <c r="H50" s="128"/>
-      <c r="I50" s="128"/>
-      <c r="J50" s="128"/>
-      <c r="K50" s="128"/>
-      <c r="L50" s="128"/>
-      <c r="M50" s="128"/>
-      <c r="N50" s="128"/>
-      <c r="O50" s="128"/>
-      <c r="P50" s="128"/>
-      <c r="Q50" s="128"/>
-      <c r="R50" s="128"/>
-      <c r="S50" s="128"/>
-      <c r="T50" s="128"/>
-      <c r="U50" s="128"/>
-      <c r="V50" s="129"/>
-    </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="C50" s="125"/>
+      <c r="D50" s="125"/>
+      <c r="E50" s="125"/>
+      <c r="F50" s="125"/>
+      <c r="G50" s="125"/>
+      <c r="H50" s="125"/>
+      <c r="I50" s="125"/>
+      <c r="J50" s="125"/>
+      <c r="K50" s="125"/>
+      <c r="L50" s="125"/>
+      <c r="M50" s="125"/>
+      <c r="N50" s="125"/>
+      <c r="O50" s="125"/>
+      <c r="P50" s="125"/>
+      <c r="Q50" s="125"/>
+      <c r="R50" s="125"/>
+      <c r="S50" s="125"/>
+      <c r="T50" s="125"/>
+      <c r="U50" s="125"/>
+      <c r="V50" s="126"/>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B51" s="23"/>
       <c r="C51" s="24"/>
       <c r="D51" s="24"/>
@@ -23431,7 +23400,7 @@
       <c r="P51" s="24"/>
       <c r="V51" s="25"/>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B52" s="23"/>
       <c r="C52" s="122" t="s">
         <v>1</v>
@@ -23461,9 +23430,9 @@
         <v>207</v>
       </c>
       <c r="U52" s="122"/>
-      <c r="V52" s="126"/>
-    </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="V52" s="123"/>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B53" s="23"/>
       <c r="C53" s="31" t="s">
         <v>9</v>
@@ -23505,7 +23474,7 @@
       </c>
       <c r="V53" s="89"/>
     </row>
-    <row r="54" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="23"/>
       <c r="C54" s="30" t="s">
         <v>10</v>
@@ -23562,14 +23531,14 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="1:22" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="23"/>
       <c r="C55" s="30" t="s">
         <v>174</v>
       </c>
       <c r="D55" s="81">
         <f>D6/3</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E55" s="31" t="s">
         <v>175</v>
@@ -23581,7 +23550,7 @@
       </c>
       <c r="I55" s="80">
         <f>D7/10</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J55" s="31" t="s">
         <v>175</v>
@@ -23603,7 +23572,7 @@
       </c>
       <c r="Q55" s="80">
         <f>D9/3</f>
-        <v>116.66666666666667</v>
+        <v>0</v>
       </c>
       <c r="R55" s="31" t="s">
         <v>175</v>
@@ -23619,7 +23588,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="56" spans="1:22" s="52" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:22" s="52" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="48"/>
       <c r="B56" s="49"/>
       <c r="C56" s="50" t="s">
@@ -23667,7 +23636,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:22" s="52" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:22" s="52" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="48"/>
       <c r="B57" s="23"/>
       <c r="C57" s="47"/>
@@ -23691,7 +23660,7 @@
       <c r="U57" s="60"/>
       <c r="V57" s="51"/>
     </row>
-    <row r="58" spans="1:22" s="52" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:22" s="52" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="48"/>
       <c r="B58" s="23"/>
       <c r="C58" s="24"/>
@@ -23715,7 +23684,7 @@
       <c r="U58" s="48"/>
       <c r="V58" s="51"/>
     </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B59" s="23"/>
       <c r="C59" s="24"/>
       <c r="D59" s="24"/>
@@ -23733,7 +23702,7 @@
       <c r="P59" s="24"/>
       <c r="V59" s="25"/>
     </row>
-    <row r="60" spans="1:22" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:22" s="24" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B60" s="23"/>
       <c r="C60" s="122" t="s">
         <v>184</v>
@@ -23743,11 +23712,11 @@
       <c r="F60" s="82"/>
       <c r="V60" s="25"/>
     </row>
-    <row r="61" spans="1:22" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:22" s="24" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B61" s="23"/>
       <c r="V61" s="25"/>
     </row>
-    <row r="62" spans="1:22" s="24" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:22" s="24" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B62" s="23"/>
       <c r="C62" s="60" t="s">
         <v>181</v>
@@ -23758,7 +23727,7 @@
       </c>
       <c r="V62" s="25"/>
     </row>
-    <row r="63" spans="1:22" s="24" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:22" s="24" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B63" s="23"/>
       <c r="C63" s="60" t="s">
         <v>185</v>
@@ -23769,7 +23738,7 @@
       </c>
       <c r="V63" s="25"/>
     </row>
-    <row r="64" spans="1:22" s="24" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:22" s="24" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B64" s="23"/>
       <c r="C64" s="60" t="s">
         <v>182</v>
@@ -23780,7 +23749,7 @@
       </c>
       <c r="V64" s="25"/>
     </row>
-    <row r="65" spans="2:22" s="24" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:22" s="24" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B65" s="26"/>
       <c r="C65" s="22"/>
       <c r="D65" s="22"/>
@@ -23803,13 +23772,13 @@
       <c r="U65" s="22"/>
       <c r="V65" s="27"/>
     </row>
-    <row r="66" spans="2:22" s="24" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="2:22" s="24" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="2:22" s="24" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="2:22" s="24" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="2:22" s="24" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="2:22" s="24" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="2:22" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:22" s="24" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="67" spans="2:22" s="24" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="68" spans="2:22" s="24" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:22" s="24" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="70" spans="2:22" s="24" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="71" spans="2:22" s="24" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="72" spans="2:22" s="24" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B72" s="21"/>
       <c r="C72" s="21"/>
       <c r="D72" s="21"/>
@@ -23826,7 +23795,7 @@
       <c r="O72" s="21"/>
       <c r="P72" s="21"/>
     </row>
-    <row r="73" spans="2:22" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:22" s="24" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B73" s="21"/>
       <c r="C73" s="21"/>
       <c r="D73" s="21"/>
@@ -23845,6 +23814,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L52:N52"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="H22:J22"/>
     <mergeCell ref="P52:R52"/>
     <mergeCell ref="T52:V52"/>
     <mergeCell ref="G3:J3"/>
@@ -23858,11 +23832,6 @@
     <mergeCell ref="H31:J31"/>
     <mergeCell ref="C52:E52"/>
     <mergeCell ref="H52:J52"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L52:N52"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -23907,9 +23876,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B956EFC-C7D2-4042-961D-0867141FF08C}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="8.85546875" style="21"/>
+    <col min="1" max="16384" width="8.88671875" style="21"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23921,15 +23890,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07E03289-C83F-4482-8B26-9A879D6E09A4}">
   <dimension ref="B2:H46"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="B2" s="70" t="s">
         <v>92</v>
       </c>
@@ -23940,7 +23909,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>167</v>
       </c>
@@ -23957,7 +23926,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
         <v>49</v>
       </c>
@@ -23979,7 +23948,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>51</v>
       </c>
@@ -24001,7 +23970,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>53</v>
       </c>
@@ -24022,13 +23991,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
         <v>54</v>
       </c>
       <c r="C9" s="13">
         <f>IF(SUM('Inputs Non-Residential'!D32:D37)=0,(C5/C7)*'Inputs Non-Residential'!D6,(('Inputs Non-Residential'!D32+'Inputs Non-Residential'!D33)*'Inputs Non-Residential'!D6))</f>
-        <v>330000</v>
+        <v>0</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>52</v>
@@ -24039,13 +24008,13 @@
       </c>
       <c r="G9" s="13">
         <f>IF(SUM('Inputs Non-Residential'!D39:D44)=0,(G5/G7)*'Inputs Non-Residential'!D6,(('Inputs Non-Residential'!D39+'Inputs Non-Residential'!D40)*'Inputs Non-Residential'!D6))</f>
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B10" s="6"/>
       <c r="C10" s="18"/>
       <c r="D10" s="6"/>
@@ -24053,7 +24022,7 @@
       <c r="G10" s="18"/>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="2:8" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
         <v>169</v>
       </c>
@@ -24070,7 +24039,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>49</v>
       </c>
@@ -24092,7 +24061,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13" s="6" t="s">
         <v>51</v>
       </c>
@@ -24114,7 +24083,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" s="6" t="s">
         <v>53</v>
       </c>
@@ -24135,7 +24104,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
         <v>54</v>
       </c>
@@ -24158,7 +24127,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>150</v>
       </c>
@@ -24167,14 +24136,14 @@
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="1"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
         <v>151</v>
       </c>
@@ -24197,7 +24166,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="9" t="s">
         <v>63</v>
       </c>
@@ -24214,7 +24183,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="6" t="s">
         <v>64</v>
       </c>
@@ -24235,7 +24204,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="6" t="s">
         <v>104</v>
       </c>
@@ -24255,13 +24224,13 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="7" t="s">
         <v>67</v>
       </c>
       <c r="C27" s="13">
         <f>IF('Inputs Non-Residential'!D37=0,((C24/1000)*C25*'Inputs Non-Residential'!D6*365),('Inputs Non-Residential'!D37*'Inputs Non-Residential'!D6))</f>
-        <v>165000</v>
+        <v>0</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>52</v>
@@ -24272,13 +24241,13 @@
       </c>
       <c r="G27" s="13">
         <f>IF('Inputs Non-Residential'!D44=0,((G24/1000)*G25*'Inputs Non-Residential'!D6*365),'Inputs Non-Residential'!D44*'Inputs Non-Residential'!D6)</f>
-        <v>6132</v>
+        <v>0</v>
       </c>
       <c r="H27" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="9" t="s">
         <v>69</v>
       </c>
@@ -24295,13 +24264,13 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B30" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C30" s="10">
         <f>('Inputs Non-Residential'!D55*0.26*20*4.5*365)</f>
-        <v>427050</v>
+        <v>0</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>71</v>
@@ -24311,13 +24280,13 @@
       </c>
       <c r="G30" s="10">
         <f>C30*(1-('Inputs Non-Residential'!D56/100))</f>
-        <v>427050</v>
+        <v>0</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B31" s="6" t="s">
         <v>73</v>
       </c>
@@ -24337,7 +24306,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B32" s="6" t="s">
         <v>75</v>
       </c>
@@ -24357,7 +24326,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B33" s="6" t="s">
         <v>76</v>
       </c>
@@ -24377,13 +24346,13 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B34" s="6" t="s">
         <v>78</v>
       </c>
       <c r="C34" s="10">
         <f>(C30*C33*(C32-C31))/3.6</f>
-        <v>22345.391249999997</v>
+        <v>0</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>52</v>
@@ -24393,19 +24362,19 @@
       </c>
       <c r="G34" s="10">
         <f>(G30*G33*(G32-G31))/3.6</f>
-        <v>22345.391249999997</v>
+        <v>0</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B35" s="6"/>
       <c r="D35" s="6"/>
       <c r="F35" s="6"/>
       <c r="H35" s="6"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B36" s="6" t="s">
         <v>80</v>
       </c>
@@ -24426,13 +24395,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B38" s="7" t="s">
         <v>82</v>
       </c>
       <c r="C38" s="13">
         <f>C34/C36</f>
-        <v>22345.391249999997</v>
+        <v>0</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>52</v>
@@ -24443,13 +24412,13 @@
       </c>
       <c r="G38" s="13">
         <f>G34/G36</f>
-        <v>8938.1564999999991</v>
+        <v>0</v>
       </c>
       <c r="H38" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B40" s="9" t="s">
         <v>85</v>
       </c>
@@ -24460,7 +24429,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B41" s="6" t="s">
         <v>194</v>
       </c>
@@ -24475,7 +24444,7 @@
         <v>None</v>
       </c>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>157</v>
       </c>
@@ -24490,7 +24459,7 @@
         <v>Electric</v>
       </c>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>88</v>
       </c>
@@ -24513,7 +24482,7 @@
         <v>kW/h</v>
       </c>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
         <v>59</v>
       </c>
@@ -24533,7 +24502,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B46" s="8" t="s">
         <v>90</v>
       </c>
@@ -24567,15 +24536,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53EF2642-E153-4AED-9FB0-35F180787D0A}">
   <dimension ref="B3:H44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:8" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>167</v>
       </c>
@@ -24592,7 +24561,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
         <v>49</v>
       </c>
@@ -24614,7 +24583,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>51</v>
       </c>
@@ -24636,7 +24605,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>53</v>
       </c>
@@ -24657,13 +24626,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
         <v>54</v>
       </c>
       <c r="C9" s="13">
         <f>IF(SUM('Inputs Non-Residential'!I32:I33)=0,(C5*'Inputs Non-Residential'!D7)/C7,(('Inputs Non-Residential'!I32+'Inputs Non-Residential'!I33)*'Inputs Non-Residential'!D7))</f>
-        <v>1346.7741935483871</v>
+        <v>0</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>52</v>
@@ -24674,13 +24643,13 @@
       </c>
       <c r="G9" s="13">
         <f>IF(SUM('Inputs Non-Residential'!I39:I40)=0,(G5*'Inputs Non-Residential'!D7)/G7,(('Inputs Non-Residential'!I39+'Inputs Non-Residential'!I40)*'Inputs Non-Residential'!D7))</f>
-        <v>1227.9411764705883</v>
+        <v>0</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
         <v>169</v>
       </c>
@@ -24697,7 +24666,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>49</v>
       </c>
@@ -24719,7 +24688,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13" s="6" t="s">
         <v>51</v>
       </c>
@@ -24741,7 +24710,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" s="6" t="s">
         <v>53</v>
       </c>
@@ -24762,7 +24731,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
         <v>54</v>
       </c>
@@ -24785,7 +24754,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>150</v>
       </c>
@@ -24794,14 +24763,14 @@
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="1"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
         <v>151</v>
       </c>
@@ -24824,7 +24793,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="5" t="s">
         <v>56</v>
       </c>
@@ -24841,7 +24810,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="6" t="s">
         <v>86</v>
       </c>
@@ -24861,7 +24830,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="6" t="s">
         <v>59</v>
       </c>
@@ -24881,13 +24850,13 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="7" t="s">
         <v>61</v>
       </c>
       <c r="C27" s="13">
         <f>(C24/1000)*(C25+((24-C25)*0.25))*(365-104)*'Inputs Non-Residential'!D7</f>
-        <v>8613</v>
+        <v>0</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>52</v>
@@ -24898,13 +24867,13 @@
       </c>
       <c r="G27" s="13">
         <f>(G24/1000)*(G25+((24-G25)*0.25))*(365-104)*'Inputs Non-Residential'!D7</f>
-        <v>8613</v>
+        <v>0</v>
       </c>
       <c r="H27" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="9" t="s">
         <v>63</v>
       </c>
@@ -24921,7 +24890,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B30" s="6" t="s">
         <v>64</v>
       </c>
@@ -24942,7 +24911,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B31" s="6" t="s">
         <v>104</v>
       </c>
@@ -24962,13 +24931,13 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B33" s="7" t="s">
         <v>67</v>
       </c>
       <c r="C33" s="13">
         <f>IF('Inputs Non-Residential'!I37=0,((C30/1000)*C31*'Inputs Non-Residential'!D7*(365-104)),('Inputs Non-Residential'!I37*'Inputs Non-Residential'!D7))</f>
-        <v>2936.25</v>
+        <v>0</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>52</v>
@@ -24979,13 +24948,13 @@
       </c>
       <c r="G33" s="13">
         <f>IF('Inputs Non-Residential'!I44=0,((G30/1000)*G31*'Inputs Non-Residential'!D7*(365-104)),('Inputs Non-Residential'!I44*'Inputs Non-Residential'!D7))</f>
-        <v>2936.25</v>
+        <v>0</v>
       </c>
       <c r="H33" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B35" s="9" t="s">
         <v>69</v>
       </c>
@@ -25002,13 +24971,13 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B36" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C36" s="10">
         <f>'Inputs Non-Residential'!I55*4*(365-104)</f>
-        <v>26100</v>
+        <v>0</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>71</v>
@@ -25018,13 +24987,13 @@
       </c>
       <c r="G36" s="10">
         <f>C36*(1-('Inputs Non-Residential'!I56/100))</f>
-        <v>26100</v>
+        <v>0</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B37" s="6" t="s">
         <v>73</v>
       </c>
@@ -25044,7 +25013,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B38" s="6" t="s">
         <v>75</v>
       </c>
@@ -25064,7 +25033,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B39" s="6" t="s">
         <v>76</v>
       </c>
@@ -25084,13 +25053,13 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B40" s="6" t="s">
         <v>78</v>
       </c>
       <c r="C40" s="10">
         <f>(C36*C39*(C38-C37))/3.6</f>
-        <v>1365.6824999999999</v>
+        <v>0</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>52</v>
@@ -25100,19 +25069,19 @@
       </c>
       <c r="G40" s="10">
         <f>(G36*G39*(G38-G37))/3.6</f>
-        <v>1365.6824999999999</v>
+        <v>0</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B41" s="6"/>
       <c r="D41" s="6"/>
       <c r="F41" s="6"/>
       <c r="H41" s="6"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B42" s="6" t="s">
         <v>80</v>
       </c>
@@ -25133,13 +25102,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B44" s="7" t="s">
         <v>82</v>
       </c>
       <c r="C44" s="13">
         <f>C40/C42</f>
-        <v>1365.6824999999999</v>
+        <v>0</v>
       </c>
       <c r="D44" s="7" t="s">
         <v>52</v>
@@ -25150,7 +25119,7 @@
       </c>
       <c r="G44" s="13">
         <f>G40/G42</f>
-        <v>1365.6824999999999</v>
+        <v>0</v>
       </c>
       <c r="H44" s="7" t="s">
         <v>52</v>
@@ -25164,15 +25133,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12EE53BE-9239-41FF-899A-A0552CE0457B}">
   <dimension ref="B3:H52"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:8" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>167</v>
       </c>
@@ -25189,7 +25158,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
         <v>49</v>
       </c>
@@ -25211,7 +25180,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>51</v>
       </c>
@@ -25233,7 +25202,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>53</v>
       </c>
@@ -25254,13 +25223,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
         <v>54</v>
       </c>
       <c r="C9" s="13">
         <f>IF(SUM('Inputs Non-Residential'!M32:M33)=0,(C5*'Inputs Non-Residential'!D8)/C7,(('Inputs Non-Residential'!M32+'Inputs Non-Residential'!M33)*'Inputs Non-Residential'!D8))</f>
-        <v>4868.5613308115244</v>
+        <v>0</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>52</v>
@@ -25271,13 +25240,13 @@
       </c>
       <c r="G9" s="13">
         <f>IF(SUM('Inputs Non-Residential'!M39:M40)=0,(G5*'Inputs Non-Residential'!D8)/G7,(('Inputs Non-Residential'!M39+'Inputs Non-Residential'!M40)*'Inputs Non-Residential'!D8))</f>
-        <v>4438.982389857566</v>
+        <v>0</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
         <v>169</v>
       </c>
@@ -25294,7 +25263,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>49</v>
       </c>
@@ -25316,7 +25285,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13" s="6" t="s">
         <v>51</v>
       </c>
@@ -25338,7 +25307,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" s="6" t="s">
         <v>53</v>
       </c>
@@ -25359,13 +25328,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
         <v>54</v>
       </c>
       <c r="C17" s="13">
         <f>SUM('Inputs Non-Residential'!M34:M35)*'Inputs Non-Residential'!D8</f>
-        <v>787500</v>
+        <v>0</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>168</v>
@@ -25376,13 +25345,13 @@
       </c>
       <c r="G17" s="13">
         <f>SUM('Inputs Non-Residential'!M41:M42)*'Inputs Non-Residential'!D8</f>
-        <v>292500</v>
+        <v>0</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>150</v>
       </c>
@@ -25391,14 +25360,14 @@
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="1"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
         <v>151</v>
       </c>
@@ -25421,7 +25390,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="5" t="s">
         <v>56</v>
       </c>
@@ -25438,7 +25407,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="6" t="s">
         <v>86</v>
       </c>
@@ -25458,7 +25427,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="6" t="s">
         <v>59</v>
       </c>
@@ -25478,13 +25447,13 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="7" t="s">
         <v>61</v>
       </c>
       <c r="C27" s="13">
         <f>(C24/1000)*C25*'Inputs Non-Residential'!D8*365</f>
-        <v>6570</v>
+        <v>0</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>52</v>
@@ -25495,13 +25464,13 @@
       </c>
       <c r="G27" s="13">
         <f>(G24/1000)*G25*'Inputs Non-Residential'!D8*365</f>
-        <v>6570</v>
+        <v>0</v>
       </c>
       <c r="H27" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="9" t="s">
         <v>63</v>
       </c>
@@ -25518,7 +25487,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B30" s="6" t="s">
         <v>64</v>
       </c>
@@ -25539,7 +25508,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B31" s="6" t="s">
         <v>104</v>
       </c>
@@ -25559,13 +25528,13 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B33" s="7" t="s">
         <v>67</v>
       </c>
       <c r="C33" s="13">
         <f>IF('Inputs Non-Residential'!M37=0,((C30/1000)*C31*'Inputs Non-Residential'!D8*365),('Inputs Non-Residential'!M37*'Inputs Non-Residential'!D8))</f>
-        <v>7391.25</v>
+        <v>0</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>52</v>
@@ -25576,13 +25545,13 @@
       </c>
       <c r="G33" s="13">
         <f>IF('Inputs Non-Residential'!M44=0,((G30/1000)*G31*'Inputs Non-Residential'!D8*365),('Inputs Non-Residential'!M44*'Inputs Non-Residential'!D8))</f>
-        <v>7391.25</v>
+        <v>0</v>
       </c>
       <c r="H33" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B35" s="9" t="s">
         <v>69</v>
       </c>
@@ -25599,7 +25568,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B36" s="6" t="s">
         <v>70</v>
       </c>
@@ -25621,7 +25590,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B37" s="6" t="s">
         <v>73</v>
       </c>
@@ -25641,7 +25610,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B38" s="6" t="s">
         <v>75</v>
       </c>
@@ -25661,7 +25630,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B39" s="6" t="s">
         <v>76</v>
       </c>
@@ -25681,7 +25650,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B40" s="6" t="s">
         <v>78</v>
       </c>
@@ -25703,13 +25672,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B41" s="6"/>
       <c r="D41" s="6"/>
       <c r="F41" s="6"/>
       <c r="H41" s="6"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B42" s="6" t="s">
         <v>80</v>
       </c>
@@ -25730,7 +25699,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B44" s="7" t="s">
         <v>82</v>
       </c>
@@ -25753,7 +25722,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B46" s="9" t="s">
         <v>85</v>
       </c>
@@ -25773,7 +25742,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B47" s="6" t="s">
         <v>194</v>
       </c>
@@ -25788,7 +25757,7 @@
         <v>None</v>
       </c>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B48" s="6" t="s">
         <v>156</v>
       </c>
@@ -25803,7 +25772,7 @@
         <v>Electric</v>
       </c>
     </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>88</v>
       </c>
@@ -25826,7 +25795,7 @@
         <v>kW/h</v>
       </c>
     </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
         <v>59</v>
       </c>
@@ -25846,7 +25815,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B52" s="8" t="s">
         <v>90</v>
       </c>
@@ -25877,15 +25846,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3B192FB-29DF-4106-A631-AA1EE482C5A5}">
   <dimension ref="B3:H44"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:8" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>167</v>
       </c>
@@ -25902,7 +25871,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
         <v>49</v>
       </c>
@@ -25924,7 +25893,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>51</v>
       </c>
@@ -25946,7 +25915,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>53</v>
       </c>
@@ -25967,13 +25936,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
         <v>54</v>
       </c>
       <c r="C9" s="13">
         <f>IF(SUM('Inputs Non-Residential'!Q32:Q33)=0,(C5*'Inputs Non-Residential'!D9)/C7,(('Inputs Non-Residential'!Q32+'Inputs Non-Residential'!Q33)*'Inputs Non-Residential'!D9))</f>
-        <v>1298.9119338286555</v>
+        <v>0</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>52</v>
@@ -25984,13 +25953,13 @@
       </c>
       <c r="G9" s="13">
         <f>IF(SUM('Inputs Non-Residential'!Q39:Q40)=0,(G5*'Inputs Non-Residential'!D9)/G7,(('Inputs Non-Residential'!Q39+'Inputs Non-Residential'!Q40)*'Inputs Non-Residential'!D9))</f>
-        <v>1184.3020573143624</v>
+        <v>0</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
         <v>169</v>
       </c>
@@ -26007,7 +25976,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>49</v>
       </c>
@@ -26029,7 +25998,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13" s="6" t="s">
         <v>51</v>
       </c>
@@ -26051,7 +26020,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" s="6" t="s">
         <v>53</v>
       </c>
@@ -26072,7 +26041,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
         <v>54</v>
       </c>
@@ -26095,7 +26064,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>150</v>
       </c>
@@ -26104,14 +26073,14 @@
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="1"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
         <v>151</v>
       </c>
@@ -26134,7 +26103,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="5" t="s">
         <v>56</v>
       </c>
@@ -26151,7 +26120,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="6" t="s">
         <v>86</v>
       </c>
@@ -26171,7 +26140,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="6" t="s">
         <v>59</v>
       </c>
@@ -26191,13 +26160,13 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="7" t="s">
         <v>61</v>
       </c>
       <c r="C27" s="13">
         <f>(C24/1000)*(C25+((24-C25)*0.25))*(365-104)*'Inputs Non-Residential'!D9</f>
-        <v>12058.199999999999</v>
+        <v>0</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>52</v>
@@ -26208,13 +26177,13 @@
       </c>
       <c r="G27" s="13">
         <f>(G24/1000)*(G25+((24-G25)*0.25))*(365-104)*'Inputs Non-Residential'!D9</f>
-        <v>12058.199999999999</v>
+        <v>0</v>
       </c>
       <c r="H27" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="9" t="s">
         <v>63</v>
       </c>
@@ -26231,7 +26200,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B30" s="6" t="s">
         <v>64</v>
       </c>
@@ -26252,7 +26221,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B31" s="6" t="s">
         <v>104</v>
       </c>
@@ -26272,13 +26241,13 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B33" s="7" t="s">
         <v>67</v>
       </c>
       <c r="C33" s="13">
         <f>IF('Inputs Non-Residential'!Q37=0,((C30/1000)*C31*'Inputs Non-Residential'!D9*(365-104)),('Inputs Non-Residential'!Q37*'Inputs Non-Residential'!D9))</f>
-        <v>4110.75</v>
+        <v>0</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>52</v>
@@ -26289,13 +26258,13 @@
       </c>
       <c r="G33" s="13">
         <f>IF('Inputs Non-Residential'!Q44=0,((G30/1000)*G31*'Inputs Non-Residential'!D9*(365-104)),('Inputs Non-Residential'!Q44*'Inputs Non-Residential'!D9))</f>
-        <v>4110.75</v>
+        <v>0</v>
       </c>
       <c r="H33" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B35" s="9" t="s">
         <v>69</v>
       </c>
@@ -26312,13 +26281,13 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B36" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C36" s="10">
         <f>'Inputs Non-Residential'!Q55*4*(365-104)</f>
-        <v>121800</v>
+        <v>0</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>71</v>
@@ -26328,13 +26297,13 @@
       </c>
       <c r="G36" s="10">
         <f>C36*(1-('Inputs Non-Residential'!Q56/100))</f>
-        <v>121800</v>
+        <v>0</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B37" s="6" t="s">
         <v>73</v>
       </c>
@@ -26354,7 +26323,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B38" s="6" t="s">
         <v>75</v>
       </c>
@@ -26374,7 +26343,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B39" s="6" t="s">
         <v>76</v>
       </c>
@@ -26394,13 +26363,13 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B40" s="6" t="s">
         <v>78</v>
       </c>
       <c r="C40" s="10">
         <f>(C36*C39*(C38-C37))/3.6</f>
-        <v>6373.1849999999986</v>
+        <v>0</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>52</v>
@@ -26410,19 +26379,19 @@
       </c>
       <c r="G40" s="10">
         <f>(G36*G39*(G38-G37))/3.6</f>
-        <v>6373.1849999999986</v>
+        <v>0</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B41" s="6"/>
       <c r="D41" s="6"/>
       <c r="F41" s="6"/>
       <c r="H41" s="6"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B42" s="6" t="s">
         <v>80</v>
       </c>
@@ -26443,13 +26412,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B44" s="7" t="s">
         <v>82</v>
       </c>
       <c r="C44" s="13">
         <f>C40/C42</f>
-        <v>6373.1849999999986</v>
+        <v>0</v>
       </c>
       <c r="D44" s="7" t="s">
         <v>52</v>
@@ -26460,7 +26429,7 @@
       </c>
       <c r="G44" s="13">
         <f>G40/G42</f>
-        <v>6373.1849999999986</v>
+        <v>0</v>
       </c>
       <c r="H44" s="7" t="s">
         <v>52</v>
@@ -26474,15 +26443,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E447DEC9-400D-4C2E-96E8-F610B68FBAB8}">
   <dimension ref="B3:H52"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:8" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B3" s="5" t="s">
         <v>167</v>
       </c>
@@ -26499,7 +26468,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
         <v>49</v>
       </c>
@@ -26521,7 +26490,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>51</v>
       </c>
@@ -26543,7 +26512,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>53</v>
       </c>
@@ -26564,13 +26533,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
         <v>54</v>
       </c>
       <c r="C9" s="13">
         <f>IF(SUM('Inputs Non-Residential'!U32:U33)=0,(C5*'Inputs Non-Residential'!D10)/C7,(('Inputs Non-Residential'!U32+'Inputs Non-Residential'!U33)*'Inputs Non-Residential'!D10))</f>
-        <v>913.43407383848762</v>
+        <v>0</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>52</v>
@@ -26581,13 +26550,13 @@
       </c>
       <c r="G9" s="13">
         <f>IF(SUM('Inputs Non-Residential'!U39:U40)=0,(G5*'Inputs Non-Residential'!D10)/G7,(('Inputs Non-Residential'!U39+'Inputs Non-Residential'!U40)*'Inputs Non-Residential'!D10))</f>
-        <v>832.8369496762682</v>
+        <v>0</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" ht="27" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
         <v>169</v>
       </c>
@@ -26604,7 +26573,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>49</v>
       </c>
@@ -26626,7 +26595,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13" s="6" t="s">
         <v>51</v>
       </c>
@@ -26648,7 +26617,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" s="6" t="s">
         <v>53</v>
       </c>
@@ -26669,7 +26638,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
         <v>54</v>
       </c>
@@ -26692,7 +26661,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>150</v>
       </c>
@@ -26701,14 +26670,14 @@
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="1"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="7" t="s">
         <v>151</v>
       </c>
@@ -26731,7 +26700,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="5" t="s">
         <v>56</v>
       </c>
@@ -26748,7 +26717,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="6" t="s">
         <v>86</v>
       </c>
@@ -26768,7 +26737,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="6" t="s">
         <v>59</v>
       </c>
@@ -26788,13 +26757,13 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="7" t="s">
         <v>61</v>
       </c>
       <c r="C27" s="13">
         <f>(C24/1000)*C25*'Inputs Non-Residential'!D10*365</f>
-        <v>1460</v>
+        <v>0</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>52</v>
@@ -26805,13 +26774,13 @@
       </c>
       <c r="G27" s="13">
         <f>(G24/1000)*G25*'Inputs Non-Residential'!D10*365</f>
-        <v>1460</v>
+        <v>0</v>
       </c>
       <c r="H27" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="9" t="s">
         <v>63</v>
       </c>
@@ -26828,7 +26797,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B30" s="6" t="s">
         <v>64</v>
       </c>
@@ -26849,7 +26818,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B31" s="6" t="s">
         <v>104</v>
       </c>
@@ -26869,13 +26838,13 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B33" s="7" t="s">
         <v>67</v>
       </c>
       <c r="C33" s="13">
         <f>IF('Inputs Non-Residential'!U37=0,((C30/1000)*C31*'Inputs Non-Residential'!D10*365),('Inputs Non-Residential'!U37*'Inputs Non-Residential'!D10))</f>
-        <v>1733.75</v>
+        <v>0</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>52</v>
@@ -26886,13 +26855,13 @@
       </c>
       <c r="G33" s="13">
         <f>IF('Inputs Non-Residential'!U44=0,((G30/1000)*G31*'Inputs Non-Residential'!D10*365),('Inputs Non-Residential'!U44*'Inputs Non-Residential'!D10))</f>
-        <v>1733.75</v>
+        <v>0</v>
       </c>
       <c r="H33" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B35" s="9" t="s">
         <v>69</v>
       </c>
@@ -26909,7 +26878,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B36" s="6" t="s">
         <v>70</v>
       </c>
@@ -26931,7 +26900,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B37" s="6" t="s">
         <v>73</v>
       </c>
@@ -26951,7 +26920,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B38" s="6" t="s">
         <v>75</v>
       </c>
@@ -26971,7 +26940,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B39" s="6" t="s">
         <v>76</v>
       </c>
@@ -26991,7 +26960,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B40" s="6" t="s">
         <v>78</v>
       </c>
@@ -27013,13 +26982,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B41" s="6"/>
       <c r="D41" s="6"/>
       <c r="F41" s="6"/>
       <c r="H41" s="6"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B42" s="6" t="s">
         <v>80</v>
       </c>
@@ -27040,7 +27009,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B44" s="7" t="s">
         <v>82</v>
       </c>
@@ -27063,7 +27032,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B46" s="9" t="s">
         <v>85</v>
       </c>
@@ -27083,7 +27052,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B47" s="6" t="s">
         <v>194</v>
       </c>
@@ -27098,7 +27067,7 @@
         <v>None</v>
       </c>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B48" s="6" t="s">
         <v>156</v>
       </c>
@@ -27113,7 +27082,7 @@
         <v>Electric</v>
       </c>
     </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>88</v>
       </c>
@@ -27136,7 +27105,7 @@
         <v>kW/h</v>
       </c>
     </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
         <v>59</v>
       </c>
@@ -27156,7 +27125,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B52" s="8" t="s">
         <v>90</v>
       </c>
@@ -27188,15 +27157,15 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C9AA639-308E-451F-8C9F-E88EF1CD0A9F}">
   <dimension ref="B2:H22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="5" t="s">
         <v>139</v>
       </c>
@@ -27213,13 +27182,13 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
         <v>191</v>
       </c>
       <c r="C4" s="10">
         <f>'Inputs Non-Residential'!D11*42.33*(3212/8760)</f>
-        <v>4656.2999999999993</v>
+        <v>0</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>52</v>
@@ -27230,13 +27199,13 @@
       </c>
       <c r="G4" s="10">
         <f>'Inputs Non-Residential'!D11*42.33*(3212/8760)</f>
-        <v>4656.2999999999993</v>
+        <v>0</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5" s="6"/>
       <c r="C5" s="18"/>
       <c r="D5" s="6"/>
@@ -27244,7 +27213,7 @@
       <c r="G5" s="18"/>
       <c r="H5" s="6"/>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B6" s="9" t="s">
         <v>140</v>
       </c>
@@ -27261,7 +27230,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>64</v>
       </c>
@@ -27281,7 +27250,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
         <v>104</v>
       </c>
@@ -27301,13 +27270,13 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
         <v>67</v>
       </c>
       <c r="C10" s="13">
         <f>(C7/1000)*C8*365*'Inputs Non-Residential'!D11</f>
-        <v>2190</v>
+        <v>0</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>52</v>
@@ -27318,13 +27287,13 @@
       </c>
       <c r="G10" s="13">
         <f>(G7/1000)*G8*365*'Inputs Non-Residential'!D11</f>
-        <v>2190</v>
+        <v>0</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" s="9" t="s">
         <v>141</v>
       </c>
@@ -27341,7 +27310,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13" s="6" t="s">
         <v>64</v>
       </c>
@@ -27361,7 +27330,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="s">
         <v>104</v>
       </c>
@@ -27381,13 +27350,13 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
         <v>67</v>
       </c>
       <c r="C16" s="13">
         <f>(C13/1000)*C14*365*'Inputs Non-Residential'!D12</f>
-        <v>547.5</v>
+        <v>0</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>52</v>
@@ -27398,13 +27367,13 @@
       </c>
       <c r="G16" s="13">
         <f>(G13/1000)*G14*365*'Inputs Non-Residential'!D12</f>
-        <v>547.5</v>
+        <v>0</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="9" t="s">
         <v>136</v>
       </c>
@@ -27415,7 +27384,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>137</v>
       </c>
@@ -27437,7 +27406,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>133</v>
       </c>
@@ -27453,7 +27422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="7" t="s">
         <v>138</v>
       </c>
